--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,6 +54,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -346,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q331"/>
+  <dimension ref="A1:Q335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +575,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -582,7 +655,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -657,7 +735,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -732,7 +815,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -807,7 +895,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -882,7 +975,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -957,7 +1055,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1135,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1215,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1295,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1375,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1455,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1535,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1615,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1695,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1775,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1855,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1935,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1857,7 +2015,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -1932,7 +2095,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2175,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2255,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2335,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2415,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2495,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2575,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2655,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2735,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2815,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2895,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2750,9 +2968,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>58.9830508474576</v>
-      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -2760,7 +2975,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2828,9 +3048,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>58.6571056062582</v>
-      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -2838,7 +3055,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2906,9 +3128,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v>58.3311603650587</v>
-      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -2916,7 +3135,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -2984,9 +3208,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>58.0052151238592</v>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -2994,7 +3215,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3062,9 +3288,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>57.6792698826597</v>
-      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3072,7 +3295,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3140,9 +3368,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>57.3533246414602</v>
-      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3150,7 +3375,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3218,9 +3448,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>57.0273794002608</v>
-      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3228,7 +3455,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3296,9 +3528,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>56.7014341590613</v>
-      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3306,7 +3535,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3374,9 +3608,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>56.3754889178618</v>
-      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3384,7 +3615,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3452,9 +3688,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v>56.0495436766623</v>
-      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3462,7 +3695,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3530,9 +3768,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v>55.7235984354628</v>
-      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3540,7 +3775,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3608,9 +3848,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N43" t="n">
-        <v>55.53698769911</v>
-      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3618,7 +3855,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3686,9 +3928,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N44" t="n">
-        <v>55.3503769627572</v>
-      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3696,7 +3935,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3764,9 +4008,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N45" t="n">
-        <v>55.1637662264044</v>
-      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3774,7 +4015,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3842,9 +4088,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v>54.9771554900516</v>
-      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3852,7 +4095,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3920,9 +4168,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>54.7905447536988</v>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3930,7 +4175,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3998,9 +4248,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v>54.603934017346</v>
-      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4008,7 +4255,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4076,9 +4328,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>54.4173232809931</v>
-      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4086,7 +4335,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4154,9 +4408,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N50" t="n">
-        <v>54.2307125446403</v>
-      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4164,7 +4415,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4232,9 +4488,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N51" t="n">
-        <v>54.0441018082875</v>
-      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4242,7 +4495,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4310,9 +4568,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N52" t="n">
-        <v>53.8574910719347</v>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4320,7 +4575,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4388,9 +4648,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N53" t="n">
-        <v>53.6711070800975</v>
-      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4398,7 +4655,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4466,9 +4728,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N54" t="n">
-        <v>53.4847230882603</v>
-      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4476,7 +4735,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4544,9 +4808,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N55" t="n">
-        <v>53.2983390964231</v>
-      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4554,7 +4815,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4622,9 +4888,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N56" t="n">
-        <v>53.1119551045859</v>
-      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4632,7 +4895,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4700,9 +4968,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N57" t="n">
-        <v>52.9255711127487</v>
-      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4710,7 +4975,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4778,9 +5048,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N58" t="n">
-        <v>52.7671447196871</v>
-      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4788,7 +5055,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4856,9 +5128,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N59" t="n">
-        <v>52.6366759254011</v>
-      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4866,7 +5135,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -4934,9 +5208,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N60" t="n">
-        <v>52.5341647298906</v>
-      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4944,7 +5215,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5012,9 +5288,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N61" t="n">
-        <v>52.4596111331557</v>
-      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5022,7 +5295,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5090,9 +5368,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N62" t="n">
-        <v>52.4130151351964</v>
-      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5100,7 +5375,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5168,9 +5448,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N63" t="n">
-        <v>52.3477807380534</v>
-      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5178,7 +5455,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5246,9 +5528,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N64" t="n">
-        <v>52.2949719403662</v>
-      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5256,7 +5535,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5324,9 +5608,6 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N65" t="n">
-        <v>52.2338793719177</v>
-      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5334,7 +5615,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5695,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5775,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5816,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5534,22 +5830,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Bosques</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>electricidad</t>
+          <t>bosques</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>EG.ELC.ACCS.ZS</t>
+          <t>AG.LND.FRST.ZS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Acceso a electricidad</t>
+          <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5559,7 +5855,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5896,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5634,7 +5935,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5976,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5709,7 +6015,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5745,7 +6056,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5784,7 +6095,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5820,7 +6136,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -5859,7 +6175,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5895,7 +6216,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -5934,7 +6255,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5970,7 +6296,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -6009,7 +6335,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6376,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -6084,7 +6415,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6456,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -6159,7 +6495,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6536,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -6234,7 +6575,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6616,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6309,7 +6655,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6696,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6384,7 +6735,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6776,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -6459,7 +6815,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6856,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6534,7 +6895,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6936,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -6609,7 +6975,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6645,7 +7016,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6684,7 +7055,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6720,7 +7096,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6759,7 +7135,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6795,7 +7176,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6834,7 +7215,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6870,7 +7256,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6909,7 +7295,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6945,7 +7336,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6984,7 +7375,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7416,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7059,7 +7455,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7496,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -7134,7 +7535,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7576,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7209,7 +7615,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7656,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7284,7 +7695,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7736,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -7359,7 +7775,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7816,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -7434,7 +7855,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7896,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -7509,7 +7935,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7976,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -7584,7 +8015,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7620,7 +8056,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -7659,7 +8095,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7695,7 +8136,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7734,7 +8175,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7770,7 +8216,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7809,7 +8255,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7845,7 +8296,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7884,7 +8335,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7920,7 +8376,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7952,9 +8408,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N100" t="n">
-        <v>97.82020300000001</v>
-      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7962,7 +8415,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7998,7 +8456,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -8030,9 +8488,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N101" t="n">
-        <v>98.2395324707031</v>
-      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8040,7 +8495,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8536,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -8108,9 +8568,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N102" t="n">
-        <v>98.3233337402344</v>
-      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8118,7 +8575,12 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8616,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -8186,9 +8648,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N103" t="n">
-        <v>99</v>
-      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8196,7 +8655,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8696,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -8264,9 +8728,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N104" t="n">
-        <v>98.484130859375</v>
-      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8274,7 +8735,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8776,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -8342,9 +8808,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N105" t="n">
-        <v>98.7</v>
-      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8352,7 +8815,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8856,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -8420,9 +8888,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N106" t="n">
-        <v>98.40000000000001</v>
-      </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8430,7 +8895,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8936,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -8498,9 +8968,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N107" t="n">
-        <v>98.90000000000001</v>
-      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8508,7 +8975,12 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8544,7 +9016,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8576,9 +9048,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N108" t="n">
-        <v>98.90000000000001</v>
-      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8586,7 +9055,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8622,7 +9096,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8654,9 +9128,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N109" t="n">
-        <v>99.90000000000001</v>
-      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8664,7 +9135,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8700,7 +9176,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8732,9 +9208,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N110" t="n">
-        <v>99.8</v>
-      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8742,7 +9215,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8778,7 +9256,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8810,9 +9288,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N111" t="n">
-        <v>95.7</v>
-      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8820,7 +9295,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8856,7 +9336,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8888,9 +9368,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N112" t="n">
-        <v>99.09999999999999</v>
-      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8898,7 +9375,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8934,7 +9416,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8966,9 +9448,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N113" t="n">
-        <v>98.8</v>
-      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8976,7 +9455,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9496,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -9044,9 +9528,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N114" t="n">
-        <v>99.3</v>
-      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9054,7 +9535,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9576,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -9122,9 +9608,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N115" t="n">
-        <v>98.90000000000001</v>
-      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9132,7 +9615,12 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9656,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9200,9 +9688,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N116" t="n">
-        <v>98.90000000000001</v>
-      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9210,7 +9695,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9736,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9278,9 +9768,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N117" t="n">
-        <v>99</v>
-      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9288,7 +9775,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9816,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -9356,9 +9848,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N118" t="n">
-        <v>99.09999999999999</v>
-      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9366,7 +9855,12 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9896,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9434,9 +9928,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N119" t="n">
-        <v>98.8</v>
-      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9444,7 +9935,12 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9976,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -9512,9 +10008,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N120" t="n">
-        <v>99.3</v>
-      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9522,7 +10015,12 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9558,7 +10056,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -9590,9 +10088,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N121" t="n">
-        <v>99.40000000000001</v>
-      </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9600,7 +10095,12 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9636,7 +10136,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -9668,9 +10168,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N122" t="n">
-        <v>100</v>
-      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9678,7 +10175,12 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9714,7 +10216,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -9746,9 +10248,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N123" t="n">
-        <v>100</v>
-      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9756,7 +10255,12 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9792,7 +10296,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -9824,9 +10328,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N124" t="n">
-        <v>99.40000000000001</v>
-      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9834,7 +10335,12 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9870,7 +10376,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -9902,9 +10408,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N125" t="n">
-        <v>99.2</v>
-      </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9912,7 +10415,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9948,7 +10456,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -9980,9 +10488,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N126" t="n">
-        <v>99.90000000000001</v>
-      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9990,7 +10495,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10536,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -10058,9 +10568,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N127" t="n">
-        <v>99.8</v>
-      </c>
       <c r="O127" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10068,7 +10575,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10616,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -10136,9 +10648,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N128" t="n">
-        <v>99.90000000000001</v>
-      </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10146,7 +10655,12 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10182,7 +10696,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -10214,9 +10728,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N129" t="n">
-        <v>100</v>
-      </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10224,7 +10735,12 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10776,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -10292,9 +10808,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N130" t="n">
-        <v>100</v>
-      </c>
       <c r="O130" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10302,7 +10815,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10856,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -10370,9 +10888,6 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N131" t="n">
-        <v>100</v>
-      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10380,7 +10895,12 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10936,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -10455,7 +10975,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10491,7 +11016,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -10530,7 +11055,12 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10566,7 +11096,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -10590,12 +11120,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>EG.ELC.RNEW.ZS</t>
+          <t>EG.ELC.ACCS.ZS</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
+          <t>Acceso a electricidad</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10605,7 +11135,12 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10641,7 +11176,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1961</v>
+        <v>2026</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -10665,12 +11200,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>EG.ELC.RNEW.ZS</t>
+          <t>EG.ELC.ACCS.ZS</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
+          <t>Acceso a electricidad</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10680,7 +11215,12 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10716,7 +11256,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -10755,7 +11295,12 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10791,7 +11336,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -10830,7 +11375,12 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10866,7 +11416,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10905,7 +11455,12 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10941,7 +11496,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -10980,7 +11535,12 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11576,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -11055,7 +11615,12 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11656,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -11130,7 +11695,12 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11736,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -11205,7 +11775,12 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11816,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11280,7 +11855,12 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11896,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11355,7 +11935,12 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11976,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -11430,7 +12015,12 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11466,7 +12056,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -11505,7 +12095,12 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11541,7 +12136,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -11580,7 +12175,12 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11616,7 +12216,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -11655,7 +12255,12 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11691,7 +12296,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -11730,7 +12335,12 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11766,7 +12376,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -11805,7 +12415,12 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11841,7 +12456,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -11880,7 +12495,12 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11916,7 +12536,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11955,7 +12575,12 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11991,7 +12616,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -12030,7 +12655,12 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12696,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -12105,7 +12735,12 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12776,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -12180,7 +12815,12 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12856,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -12255,7 +12895,12 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12936,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -12330,7 +12975,12 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12366,7 +13016,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -12405,7 +13055,12 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12441,7 +13096,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12480,7 +13135,12 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12516,7 +13176,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -12555,7 +13215,12 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12591,7 +13256,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -12630,7 +13295,12 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12666,7 +13336,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -12705,7 +13375,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12741,7 +13416,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -12780,7 +13455,12 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12816,7 +13496,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -12848,9 +13528,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N164" t="n">
-        <v>62.3438579929536</v>
-      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12858,7 +13535,12 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12894,7 +13576,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -12926,9 +13608,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N165" t="n">
-        <v>70.3254022135561</v>
-      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12936,7 +13615,12 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12972,7 +13656,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -13004,9 +13688,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N166" t="n">
-        <v>70.09341637010679</v>
-      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13014,7 +13695,12 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13736,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -13082,9 +13768,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N167" t="n">
-        <v>68.42985212302899</v>
-      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13092,7 +13775,12 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13128,7 +13816,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -13160,9 +13848,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N168" t="n">
-        <v>72.0068519116553</v>
-      </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13170,7 +13855,12 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13206,7 +13896,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -13238,9 +13928,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N169" t="n">
-        <v>70.0514663834654</v>
-      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13248,7 +13935,12 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13976,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -13316,9 +14008,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N170" t="n">
-        <v>71.237498015558</v>
-      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13326,7 +14015,12 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13362,7 +14056,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -13394,9 +14088,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N171" t="n">
-        <v>73.359380003843</v>
-      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13404,7 +14095,12 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13440,7 +14136,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -13472,9 +14168,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N172" t="n">
-        <v>71.59649946849279</v>
-      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13482,7 +14175,12 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13518,7 +14216,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -13550,9 +14248,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N173" t="n">
-        <v>75.1646552472619</v>
-      </c>
       <c r="O173" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13560,7 +14255,12 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13596,7 +14296,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -13628,9 +14328,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N174" t="n">
-        <v>73.7484021531353</v>
-      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13638,7 +14335,12 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13674,7 +14376,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -13706,9 +14408,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N175" t="n">
-        <v>67.0679878826884</v>
-      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13716,7 +14415,12 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13752,7 +14456,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -13784,9 +14488,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N176" t="n">
-        <v>64.8151373949397</v>
-      </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13794,7 +14495,12 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13830,7 +14536,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -13862,9 +14568,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N177" t="n">
-        <v>65.83572609414431</v>
-      </c>
       <c r="O177" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13872,7 +14575,12 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13908,7 +14616,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -13940,9 +14648,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N178" t="n">
-        <v>70.94119195375541</v>
-      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13950,7 +14655,12 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13986,7 +14696,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -14018,9 +14728,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N179" t="n">
-        <v>73.28606809382831</v>
-      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14028,7 +14735,12 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14776,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -14096,9 +14808,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N180" t="n">
-        <v>73.9008893155349</v>
-      </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14106,7 +14815,12 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14856,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -14174,9 +14888,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N181" t="n">
-        <v>72.7246397114189</v>
-      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14184,7 +14895,12 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14936,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -14252,9 +14968,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N182" t="n">
-        <v>72.7965497875051</v>
-      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14262,7 +14975,12 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14298,7 +15016,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -14330,9 +15048,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N183" t="n">
-        <v>71.6609231333517</v>
-      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14340,7 +15055,12 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14376,7 +15096,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -14408,9 +15128,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N184" t="n">
-        <v>67.242625937084</v>
-      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14418,7 +15135,12 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14454,7 +15176,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -14486,9 +15208,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N185" t="n">
-        <v>70.7004672541846</v>
-      </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14496,7 +15215,12 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14532,7 +15256,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -14564,9 +15288,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N186" t="n">
-        <v>67.0600784236679</v>
-      </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14574,7 +15295,12 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14610,7 +15336,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -14642,9 +15368,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N187" t="n">
-        <v>65.96440553278519</v>
-      </c>
       <c r="O187" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14652,7 +15375,12 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14688,7 +15416,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -14720,9 +15448,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N188" t="n">
-        <v>77.5369122989602</v>
-      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14730,7 +15455,12 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14766,7 +15496,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -14798,9 +15528,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N189" t="n">
-        <v>65.53966478494149</v>
-      </c>
       <c r="O189" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14808,7 +15535,12 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14844,7 +15576,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -14876,9 +15608,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N190" t="n">
-        <v>62.32403609516</v>
-      </c>
       <c r="O190" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14886,7 +15615,12 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14922,7 +15656,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -14954,9 +15688,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N191" t="n">
-        <v>51.4746640846626</v>
-      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14964,7 +15695,12 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15736,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -15032,9 +15768,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N192" t="n">
-        <v>63.2932794208759</v>
-      </c>
       <c r="O192" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15042,7 +15775,12 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15816,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -15110,9 +15848,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N193" t="n">
-        <v>65.9218035546249</v>
-      </c>
       <c r="O193" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15120,7 +15855,12 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15896,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -15188,9 +15928,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N194" t="n">
-        <v>84.45121523562889</v>
-      </c>
       <c r="O194" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15198,7 +15935,12 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15976,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -15266,9 +16008,6 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N195" t="n">
-        <v>81.72207575243419</v>
-      </c>
       <c r="O195" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15276,7 +16015,12 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15312,7 +16056,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -15351,7 +16095,12 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15387,7 +16136,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -15426,7 +16175,12 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15462,7 +16216,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -15501,7 +16255,12 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15537,7 +16296,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -15576,7 +16335,12 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15612,7 +16376,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1960</v>
+        <v>2024</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -15626,22 +16390,22 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15651,7 +16415,12 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15687,7 +16456,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1961</v>
+        <v>2025</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -15701,22 +16470,22 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15726,7 +16495,12 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15762,7 +16536,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1962</v>
+        <v>2026</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -15776,22 +16550,22 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15801,7 +16575,12 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15837,7 +16616,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -15876,7 +16655,12 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15912,7 +16696,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -15951,7 +16735,12 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15987,7 +16776,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -16026,7 +16815,12 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16856,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -16101,7 +16895,12 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16137,7 +16936,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -16176,7 +16975,12 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16212,7 +17016,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -16251,7 +17055,12 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16287,7 +17096,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -16326,7 +17135,12 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16362,7 +17176,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -16401,7 +17215,12 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16437,7 +17256,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -16476,7 +17295,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16512,7 +17336,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -16551,7 +17375,12 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16587,7 +17416,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -16626,7 +17455,12 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16662,7 +17496,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -16701,7 +17535,12 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16737,7 +17576,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -16776,7 +17615,12 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16812,7 +17656,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -16851,7 +17695,12 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16887,7 +17736,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -16926,7 +17775,12 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16962,7 +17816,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -17001,7 +17855,12 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17037,7 +17896,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -17076,7 +17935,12 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17976,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -17151,7 +18015,12 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17187,7 +18056,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -17226,7 +18095,12 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17262,7 +18136,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -17301,7 +18175,12 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17337,7 +18216,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -17376,7 +18255,12 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17412,7 +18296,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -17451,7 +18335,12 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17487,7 +18376,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -17526,7 +18415,12 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17562,7 +18456,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -17601,7 +18495,12 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17637,7 +18536,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -17676,7 +18575,12 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17712,7 +18616,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -17751,7 +18655,12 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17787,7 +18696,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -17826,7 +18735,12 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17862,7 +18776,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -17894,9 +18808,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N230" t="n">
-        <v>1997.56479057799</v>
-      </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17904,7 +18815,12 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17940,7 +18856,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -17972,9 +18888,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N231" t="n">
-        <v>2037.30182520885</v>
-      </c>
       <c r="O231" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17982,7 +18895,12 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18018,7 +18936,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -18050,9 +18968,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N232" t="n">
-        <v>2226.55481105961</v>
-      </c>
       <c r="O232" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18060,7 +18975,12 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18096,7 +19016,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -18128,9 +19048,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N233" t="n">
-        <v>2027.59967205093</v>
-      </c>
       <c r="O233" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18138,7 +19055,12 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18174,7 +19096,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -18206,9 +19128,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N234" t="n">
-        <v>2299.11785137022</v>
-      </c>
       <c r="O234" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18216,7 +19135,12 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18252,7 +19176,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -18284,9 +19208,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N235" t="n">
-        <v>2111.33770063193</v>
-      </c>
       <c r="O235" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18294,7 +19215,12 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18330,7 +19256,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -18362,9 +19288,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N236" t="n">
-        <v>2203.62644762536</v>
-      </c>
       <c r="O236" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18372,7 +19295,12 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18408,7 +19336,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -18440,9 +19368,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N237" t="n">
-        <v>2149.90770739915</v>
-      </c>
       <c r="O237" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18450,7 +19375,12 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18486,7 +19416,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -18518,9 +19448,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N238" t="n">
-        <v>2218.43187719732</v>
-      </c>
       <c r="O238" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18528,7 +19455,12 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18564,7 +19496,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -18596,9 +19528,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N239" t="n">
-        <v>2399.16210710328</v>
-      </c>
       <c r="O239" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18606,7 +19535,12 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18642,7 +19576,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -18674,9 +19608,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N240" t="n">
-        <v>2391.36796026802</v>
-      </c>
       <c r="O240" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18684,7 +19615,12 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18720,7 +19656,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -18752,9 +19688,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N241" t="n">
-        <v>2188.40606705914</v>
-      </c>
       <c r="O241" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18762,7 +19695,12 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18798,7 +19736,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -18830,9 +19768,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N242" t="n">
-        <v>2648.88652521803</v>
-      </c>
       <c r="O242" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18840,7 +19775,12 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18876,7 +19816,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -18908,9 +19848,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N243" t="n">
-        <v>2432.12630470112</v>
-      </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18918,7 +19855,12 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18954,7 +19896,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -18986,9 +19928,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N244" t="n">
-        <v>2305.02805179379</v>
-      </c>
       <c r="O244" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18996,7 +19935,12 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19976,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -19064,9 +20008,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N245" t="n">
-        <v>2371.58340737061</v>
-      </c>
       <c r="O245" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19074,7 +20015,12 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19110,7 +20056,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -19142,9 +20088,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N246" t="n">
-        <v>2377.64028480756</v>
-      </c>
       <c r="O246" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19152,7 +20095,12 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19188,7 +20136,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -19220,9 +20168,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N247" t="n">
-        <v>2391.33788149518</v>
-      </c>
       <c r="O247" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19230,7 +20175,12 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19266,7 +20216,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -19298,9 +20248,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N248" t="n">
-        <v>2346.01163837283</v>
-      </c>
       <c r="O248" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19308,7 +20255,12 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19344,7 +20296,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -19376,9 +20328,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N249" t="n">
-        <v>2231.75458660546</v>
-      </c>
       <c r="O249" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19386,7 +20335,12 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19422,7 +20376,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -19454,9 +20408,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N250" t="n">
-        <v>2621.20702328211</v>
-      </c>
       <c r="O250" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19464,7 +20415,12 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19500,7 +20456,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -19532,9 +20488,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N251" t="n">
-        <v>2309.9066118944</v>
-      </c>
       <c r="O251" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19542,7 +20495,12 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19578,7 +20536,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -19610,9 +20568,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N252" t="n">
-        <v>2310.75269478151</v>
-      </c>
       <c r="O252" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19620,7 +20575,12 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19656,7 +20616,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -19688,9 +20648,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N253" t="n">
-        <v>2529.2097489945</v>
-      </c>
       <c r="O253" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19698,7 +20655,12 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19734,7 +20696,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -19766,9 +20728,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N254" t="n">
-        <v>2173.57093050952</v>
-      </c>
       <c r="O254" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19776,7 +20735,12 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19812,7 +20776,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -19844,9 +20808,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N255" t="n">
-        <v>2098.46944015591</v>
-      </c>
       <c r="O255" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19854,7 +20815,12 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19890,7 +20856,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -19922,9 +20888,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N256" t="n">
-        <v>2009.0681450604</v>
-      </c>
       <c r="O256" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19932,7 +20895,12 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19968,7 +20936,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -20000,9 +20968,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N257" t="n">
-        <v>1933.19114696252</v>
-      </c>
       <c r="O257" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20010,7 +20975,12 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20046,7 +21016,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -20078,9 +21048,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N258" t="n">
-        <v>1451.3949056587</v>
-      </c>
       <c r="O258" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20088,7 +21055,12 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20124,7 +21096,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -20156,9 +21128,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N259" t="n">
-        <v>1379.73439965</v>
-      </c>
       <c r="O259" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20166,7 +21135,12 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20202,7 +21176,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -20234,9 +21208,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N260" t="n">
-        <v>1093.43160664363</v>
-      </c>
       <c r="O260" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20244,7 +21215,12 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20280,7 +21256,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -20312,9 +21288,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N261" t="n">
-        <v>1409.82623845927</v>
-      </c>
       <c r="O261" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20322,7 +21295,12 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20358,7 +21336,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -20390,9 +21368,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N262" t="n">
-        <v>1364.68351163595</v>
-      </c>
       <c r="O262" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20400,7 +21375,12 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20436,7 +21416,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -20468,9 +21448,6 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N263" t="n">
-        <v>1331.23284099658</v>
-      </c>
       <c r="O263" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20478,7 +21455,12 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20514,7 +21496,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -20553,7 +21535,12 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20589,7 +21576,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -20628,7 +21615,12 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20664,7 +21656,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>1960</v>
+        <v>2023</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -20678,22 +21670,22 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Recursos naturales</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>recursos_naturales</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20703,7 +21695,12 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20739,7 +21736,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>1961</v>
+        <v>2024</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -20753,22 +21750,22 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Recursos naturales</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>recursos_naturales</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -20778,7 +21775,12 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20814,7 +21816,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1962</v>
+        <v>2025</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -20828,22 +21830,22 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Recursos naturales</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>recursos_naturales</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -20853,7 +21855,12 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20889,7 +21896,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1963</v>
+        <v>2026</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -20903,22 +21910,22 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Recursos naturales</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>recursos_naturales</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -20928,7 +21935,12 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20964,7 +21976,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1964</v>
+        <v>1960</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -21003,7 +22015,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21039,7 +22051,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1965</v>
+        <v>1961</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -21078,7 +22090,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21114,7 +22126,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -21153,7 +22165,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21189,7 +22201,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -21228,7 +22240,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21264,7 +22276,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1968</v>
+        <v>1964</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -21303,7 +22315,7 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21339,7 +22351,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1969</v>
+        <v>1965</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -21378,7 +22390,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21414,7 +22426,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>1970</v>
+        <v>1966</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -21446,9 +22458,6 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N276" t="n">
-        <v>5.48772130601331</v>
-      </c>
       <c r="O276" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21456,7 +22465,7 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21492,7 +22501,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1971</v>
+        <v>1967</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -21524,9 +22533,6 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N277" t="n">
-        <v>7.38794104909662</v>
-      </c>
       <c r="O277" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21534,7 +22540,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21570,7 +22576,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -21602,9 +22608,6 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N278" t="n">
-        <v>7.19271915747182</v>
-      </c>
       <c r="O278" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21612,7 +22615,7 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21648,7 +22651,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -21680,9 +22683,6 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N279" t="n">
-        <v>10.7554427076038</v>
-      </c>
       <c r="O279" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21690,7 +22690,7 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21726,7 +22726,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1974</v>
+        <v>1970</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -21759,7 +22759,7 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>33.9478841729493</v>
+        <v>5.48772130601331</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -21768,7 +22768,7 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21804,7 +22804,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -21837,7 +22837,7 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>24.8915014056924</v>
+        <v>7.38794104909662</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -21846,7 +22846,7 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21882,7 +22882,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1976</v>
+        <v>1972</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -21915,7 +22915,7 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>22.9931513860828</v>
+        <v>7.19271915747182</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -21924,7 +22924,7 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21960,7 +22960,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -21993,7 +22993,7 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>16.1985343555775</v>
+        <v>10.7554427076038</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -22002,7 +23002,7 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22038,7 +23038,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -22071,7 +23071,7 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>15.8263995123574</v>
+        <v>33.9478841729493</v>
       </c>
       <c r="O284" t="inlineStr">
         <is>
@@ -22080,7 +23080,7 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22116,7 +23116,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -22149,7 +23149,7 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>36.481380981255</v>
+        <v>24.8915014056924</v>
       </c>
       <c r="O285" t="inlineStr">
         <is>
@@ -22158,7 +23158,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22194,7 +23194,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>1980</v>
+        <v>1976</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -22227,7 +23227,7 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>34.4312946645093</v>
+        <v>22.9931513860828</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -22236,7 +23236,7 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22272,7 +23272,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -22305,7 +23305,7 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>24.750858904318</v>
+        <v>16.1985343555775</v>
       </c>
       <c r="O287" t="inlineStr">
         <is>
@@ -22314,7 +23314,7 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22350,7 +23350,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -22383,7 +23383,7 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>13.1086608763643</v>
+        <v>15.8263995123574</v>
       </c>
       <c r="O288" t="inlineStr">
         <is>
@@ -22392,7 +23392,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22428,7 +23428,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1983</v>
+        <v>1979</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -22461,7 +23461,7 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>17.0995109701258</v>
+        <v>36.481380981255</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -22470,7 +23470,7 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22506,7 +23506,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1984</v>
+        <v>1980</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -22539,7 +23539,7 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>19.0260300794035</v>
+        <v>34.4312946645093</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -22548,7 +23548,7 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22584,7 +23584,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>1985</v>
+        <v>1981</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -22617,7 +23617,7 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>16.3107385078032</v>
+        <v>24.750858904318</v>
       </c>
       <c r="O291" t="inlineStr">
         <is>
@@ -22626,7 +23626,7 @@
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22662,7 +23662,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1986</v>
+        <v>1982</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -22695,7 +23695,7 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>8.00102414924425</v>
+        <v>13.1086608763643</v>
       </c>
       <c r="O292" t="inlineStr">
         <is>
@@ -22704,7 +23704,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22740,7 +23740,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>1987</v>
+        <v>1983</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -22773,7 +23773,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>15.9166311155573</v>
+        <v>17.0995109701258</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -22782,7 +23782,7 @@
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22818,7 +23818,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1988</v>
+        <v>1984</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -22851,7 +23851,7 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>10.0130859589153</v>
+        <v>19.0260300794035</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -22860,7 +23860,7 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22896,7 +23896,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1989</v>
+        <v>1985</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -22929,7 +23929,7 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>20.9626504331607</v>
+        <v>16.3107385078032</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -22938,7 +23938,7 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22974,7 +23974,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1990</v>
+        <v>1986</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -23007,7 +24007,7 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>29.2548511239111</v>
+        <v>8.00102414924425</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -23016,7 +24016,7 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23052,7 +24052,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1991</v>
+        <v>1987</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -23085,7 +24085,7 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>16.6639894189064</v>
+        <v>15.9166311155573</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -23094,7 +24094,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23130,7 +24130,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>1992</v>
+        <v>1988</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -23163,7 +24163,7 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>15.7571776112482</v>
+        <v>10.0130859589153</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -23172,7 +24172,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23208,7 +24208,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -23241,7 +24241,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>15.7932181812518</v>
+        <v>20.9626504331607</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -23250,7 +24250,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23286,7 +24286,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -23319,7 +24319,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>16.2198265911409</v>
+        <v>29.2548511239111</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -23328,7 +24328,7 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23364,7 +24364,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -23397,7 +24397,7 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>15.1363210095652</v>
+        <v>16.6639894189064</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
@@ -23406,7 +24406,7 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23442,7 +24442,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -23475,7 +24475,7 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>23.8367720643582</v>
+        <v>15.7571776112482</v>
       </c>
       <c r="O302" t="inlineStr">
         <is>
@@ -23484,7 +24484,7 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23520,7 +24520,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -23553,7 +24553,7 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>18.0963540802062</v>
+        <v>15.7932181812518</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -23562,7 +24562,7 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23598,7 +24598,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -23631,7 +24631,7 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>9.06347009522954</v>
+        <v>16.2198265911409</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -23640,7 +24640,7 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23676,7 +24676,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -23709,7 +24709,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>13.269532614572</v>
+        <v>15.1363210095652</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -23718,7 +24718,7 @@
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23754,7 +24754,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -23787,7 +24787,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>20.5761295010598</v>
+        <v>23.8367720643582</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -23796,7 +24796,7 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23832,7 +24832,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -23865,7 +24865,7 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>15.3442903568827</v>
+        <v>18.0963540802062</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -23874,7 +24874,7 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23910,7 +24910,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -23943,7 +24943,7 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>19.4545884689745</v>
+        <v>9.06347009522954</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -23952,7 +24952,7 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23988,7 +24988,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -24021,7 +25021,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>21.8955843439596</v>
+        <v>13.269532614572</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -24030,7 +25030,7 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24066,7 +25066,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -24099,7 +25099,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>23.8297115705399</v>
+        <v>20.5761295010598</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -24108,7 +25108,7 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24144,7 +25144,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -24177,7 +25177,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>29.2230041014033</v>
+        <v>15.3442903568827</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -24186,7 +25186,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24222,7 +25222,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -24255,7 +25255,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>28.0774680117788</v>
+        <v>19.4545884689745</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -24264,7 +25264,7 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24300,7 +25300,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -24333,7 +25333,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>23.1186941835454</v>
+        <v>21.8955843439596</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -24342,7 +25342,7 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24378,7 +25378,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -24411,7 +25411,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>23.9223070628002</v>
+        <v>23.8297115705399</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -24420,7 +25420,7 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24456,7 +25456,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -24489,7 +25489,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>10.5416668243022</v>
+        <v>29.2230041014033</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -24498,7 +25498,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24534,7 +25534,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -24567,7 +25567,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>12.380878328857</v>
+        <v>28.0774680117788</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -24576,7 +25576,7 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24612,7 +25612,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -24645,7 +25645,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>24.4753357613612</v>
+        <v>23.1186941835454</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -24654,7 +25654,7 @@
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24690,7 +25690,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -24723,7 +25723,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>18.7812359044725</v>
+        <v>23.9223070628002</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -24732,7 +25732,7 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24768,7 +25768,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -24801,7 +25801,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>17.6253449138361</v>
+        <v>10.5416668243022</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -24810,7 +25810,7 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24846,7 +25846,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -24879,7 +25879,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>11.8465082797294</v>
+        <v>12.380878328857</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -24888,7 +25888,7 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24924,7 +25924,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -24956,6 +25956,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N321" t="n">
+        <v>24.4753357613612</v>
+      </c>
       <c r="O321" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24963,7 +25966,7 @@
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24999,7 +26002,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -25031,6 +26034,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N322" t="n">
+        <v>18.7812359044725</v>
+      </c>
       <c r="O322" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25038,7 +26044,7 @@
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25074,7 +26080,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -25106,6 +26112,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N323" t="n">
+        <v>17.6253449138361</v>
+      </c>
       <c r="O323" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25113,7 +26122,7 @@
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25149,7 +26158,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -25181,6 +26190,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
+      <c r="N324" t="n">
+        <v>11.8465082797294</v>
+      </c>
       <c r="O324" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25188,7 +26200,7 @@
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25224,7 +26236,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -25263,7 +26275,7 @@
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25299,7 +26311,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -25338,7 +26350,7 @@
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25374,7 +26386,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -25413,7 +26425,7 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25449,7 +26461,7 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -25488,7 +26500,7 @@
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25524,7 +26536,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -25563,7 +26575,7 @@
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25599,7 +26611,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -25638,7 +26650,7 @@
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25674,46 +26686,346 @@
         </is>
       </c>
       <c r="G331" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Recursos naturales</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>recursos_naturales</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>NY.GDP.TOTL.RT.ZS</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Recursos naturales</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>recursos_naturales</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>NY.GDP.TOTL.RT.ZS</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Recursos naturales</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>recursos_naturales</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>NY.GDP.TOTL.RT.ZS</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Recursos naturales</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>recursos_naturales</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>NY.GDP.TOTL.RT.ZS</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
         <v>2025</v>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>Energía y ambiente</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>energia_y_ambiente</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
         <is>
           <t>Recursos naturales</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="K335" t="inlineStr">
         <is>
           <t>recursos_naturales</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="L335" t="inlineStr">
         <is>
           <t>NY.GDP.TOTL.RT.ZS</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="M335" t="inlineStr">
         <is>
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="O331" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25763,7 +27075,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25784,7 +27096,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -678,7 +693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -759,7 +774,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -840,7 +855,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -921,7 +936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1002,7 +1017,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1083,7 +1098,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1164,7 +1179,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1245,7 +1260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1326,7 +1341,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1407,7 +1422,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1488,7 +1503,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1569,7 +1584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1650,7 +1665,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1731,7 +1746,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1812,7 +1827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1893,7 +1908,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1974,7 +1989,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2055,7 +2070,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2136,7 +2151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2217,7 +2232,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2298,7 +2313,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2379,7 +2394,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2460,7 +2475,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2541,7 +2556,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2622,7 +2637,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2703,7 +2718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2784,7 +2799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2865,7 +2880,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2946,7 +2961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3027,7 +3042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3108,7 +3123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3189,7 +3204,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3270,7 +3285,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3351,7 +3366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3432,7 +3447,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3513,7 +3528,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3594,7 +3609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3675,7 +3690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3756,7 +3771,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3837,7 +3852,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3918,7 +3933,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3999,7 +4014,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -4080,7 +4095,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4161,7 +4176,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4242,7 +4257,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4323,7 +4338,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4404,7 +4419,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4485,7 +4500,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4566,7 +4581,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4647,7 +4662,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4728,7 +4743,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4809,7 +4824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4890,7 +4905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4971,7 +4986,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -5052,7 +5067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -5133,7 +5148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5214,7 +5229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5295,7 +5310,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5376,7 +5391,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5457,7 +5472,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5538,7 +5553,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5619,7 +5634,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5700,7 +5715,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5781,7 +5796,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5862,7 +5877,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5943,7 +5958,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -6024,7 +6039,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -6105,7 +6120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6186,7 +6201,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6267,7 +6282,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6348,7 +6363,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6429,7 +6444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6510,7 +6525,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6591,7 +6606,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6672,7 +6687,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6753,7 +6768,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6834,7 +6849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6915,7 +6930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6996,7 +7011,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -7077,7 +7092,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -7158,7 +7173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7239,7 +7254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7320,7 +7335,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7401,7 +7416,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7482,7 +7497,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7563,7 +7578,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7644,7 +7659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7725,7 +7740,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7806,7 +7821,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7887,7 +7902,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7968,7 +7983,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -8049,7 +8064,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -8130,7 +8145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -8211,7 +8226,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8292,7 +8307,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8373,7 +8388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8454,7 +8469,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8535,7 +8550,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8616,7 +8631,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8697,7 +8712,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8778,7 +8793,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8859,7 +8874,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8940,7 +8955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -9021,7 +9036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -9102,7 +9117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -9183,7 +9198,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9264,7 +9279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9345,7 +9360,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9426,7 +9441,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9507,7 +9522,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9588,7 +9603,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9669,7 +9684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9750,7 +9765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9831,7 +9846,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9912,7 +9927,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9993,7 +10008,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -10074,7 +10089,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -10155,7 +10170,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10236,7 +10251,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10317,7 +10332,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10398,7 +10413,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10479,7 +10494,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10560,7 +10575,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10641,7 +10656,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10722,7 +10737,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10803,7 +10818,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10884,7 +10899,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10965,7 +10980,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -11046,7 +11061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -11127,7 +11142,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11208,7 +11223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11289,7 +11304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11370,7 +11385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11451,7 +11466,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11532,7 +11547,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11613,7 +11628,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11694,7 +11709,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11775,7 +11790,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11856,7 +11871,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11937,7 +11952,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -12018,7 +12033,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -12099,7 +12114,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -12180,7 +12195,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -12261,7 +12276,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12342,7 +12357,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12423,7 +12438,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12504,7 +12519,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12585,7 +12600,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12666,7 +12681,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12747,7 +12762,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12828,7 +12843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12909,7 +12924,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12990,7 +13005,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -13071,7 +13086,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -13152,7 +13167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -13233,7 +13248,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -13314,7 +13329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13395,7 +13410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13476,7 +13491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13557,7 +13572,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13638,7 +13653,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13719,7 +13734,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13800,7 +13815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13881,7 +13896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13962,7 +13977,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -14043,7 +14058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -14124,7 +14139,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -14205,7 +14220,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -14286,7 +14301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14367,7 +14382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14448,7 +14463,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14529,7 +14544,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14610,7 +14625,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14691,7 +14706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14772,7 +14787,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14853,7 +14868,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14934,7 +14949,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -15015,7 +15030,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -15096,7 +15111,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -15177,7 +15192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -15258,7 +15273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -15339,7 +15354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15420,7 +15435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15501,7 +15516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15582,7 +15597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15663,7 +15678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15744,7 +15759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15825,7 +15840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15906,7 +15921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15987,7 +16002,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -16068,7 +16083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -16149,7 +16164,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -16230,7 +16245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -16311,7 +16326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -16392,7 +16407,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16473,7 +16488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16554,7 +16569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16635,7 +16650,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16716,7 +16731,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16797,7 +16812,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16878,7 +16893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16959,7 +16974,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -17040,7 +17055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -17121,7 +17136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -17202,7 +17217,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -17283,7 +17298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -17364,7 +17379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -17445,7 +17460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17526,7 +17541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17607,7 +17622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17688,7 +17703,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17769,7 +17784,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17850,7 +17865,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17931,7 +17946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -18012,7 +18027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -18093,7 +18108,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -18174,7 +18189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -18255,7 +18270,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -18336,7 +18351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -18417,7 +18432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18498,7 +18513,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18579,7 +18594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18660,7 +18675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18741,7 +18756,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18822,7 +18837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18903,7 +18918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18984,7 +18999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -19065,7 +19080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -19146,7 +19161,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -19227,7 +19242,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -19308,7 +19323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -19389,7 +19404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -19470,7 +19485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -19551,7 +19566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19632,7 +19647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19713,7 +19728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19794,7 +19809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19875,7 +19890,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19956,7 +19971,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -20037,7 +20052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -20118,7 +20133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -20199,7 +20214,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -20280,7 +20295,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -20361,7 +20376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -20442,7 +20457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -20523,7 +20538,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20604,7 +20619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20685,7 +20700,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20766,7 +20781,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20847,7 +20862,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20928,7 +20943,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -21009,7 +21024,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -21090,7 +21105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -21171,7 +21186,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -21252,7 +21267,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -21333,7 +21348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -21414,7 +21429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -21495,7 +21510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21576,7 +21591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21657,7 +21672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21738,7 +21753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21819,7 +21834,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21900,7 +21915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21981,7 +21996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -22062,7 +22077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -22143,7 +22158,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -22224,7 +22239,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -22305,7 +22320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -22382,7 +22397,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -22459,7 +22474,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -22536,7 +22551,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22613,7 +22628,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22690,7 +22705,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22767,7 +22782,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22844,7 +22859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22921,7 +22936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22998,7 +23013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -23075,7 +23090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -23108,7 +23123,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N285" s="4" t="n">
+      <c r="N285" s="8" t="n">
         <v>5.48772130601331</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
@@ -23154,7 +23169,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -23187,7 +23202,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N286" s="4" t="n">
+      <c r="N286" s="8" t="n">
         <v>7.38794104909662</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
@@ -23233,7 +23248,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -23266,7 +23281,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N287" s="4" t="n">
+      <c r="N287" s="8" t="n">
         <v>7.19271915747182</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
@@ -23312,7 +23327,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -23345,7 +23360,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N288" s="4" t="n">
+      <c r="N288" s="8" t="n">
         <v>10.7554427076038</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
@@ -23391,7 +23406,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -23424,7 +23439,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N289" s="4" t="n">
+      <c r="N289" s="8" t="n">
         <v>33.9478841729493</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
@@ -23470,7 +23485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -23503,7 +23518,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N290" s="4" t="n">
+      <c r="N290" s="8" t="n">
         <v>24.8915014056924</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
@@ -23549,7 +23564,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23582,7 +23597,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N291" s="4" t="n">
+      <c r="N291" s="8" t="n">
         <v>22.9931513860828</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
@@ -23628,7 +23643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23661,7 +23676,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N292" s="4" t="n">
+      <c r="N292" s="8" t="n">
         <v>16.1985343555775</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
@@ -23707,7 +23722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23740,7 +23755,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N293" s="4" t="n">
+      <c r="N293" s="8" t="n">
         <v>15.8263995123574</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
@@ -23786,7 +23801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23819,7 +23834,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N294" s="4" t="n">
+      <c r="N294" s="8" t="n">
         <v>36.481380981255</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
@@ -23865,7 +23880,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23898,7 +23913,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N295" s="4" t="n">
+      <c r="N295" s="8" t="n">
         <v>34.4312946645093</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
@@ -23944,7 +23959,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23977,7 +23992,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N296" s="4" t="n">
+      <c r="N296" s="8" t="n">
         <v>24.750858904318</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
@@ -24023,7 +24038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -24056,7 +24071,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N297" s="4" t="n">
+      <c r="N297" s="8" t="n">
         <v>13.1086608763643</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
@@ -24102,7 +24117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -24135,7 +24150,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N298" s="4" t="n">
+      <c r="N298" s="8" t="n">
         <v>17.0995109701258</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
@@ -24181,7 +24196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -24214,7 +24229,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N299" s="4" t="n">
+      <c r="N299" s="8" t="n">
         <v>19.0260300794035</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
@@ -24260,7 +24275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -24293,7 +24308,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N300" s="4" t="n">
+      <c r="N300" s="8" t="n">
         <v>16.3107385078032</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
@@ -24339,7 +24354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -24372,7 +24387,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N301" s="4" t="n">
+      <c r="N301" s="8" t="n">
         <v>8.00102414924425</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
@@ -24418,7 +24433,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -24451,7 +24466,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n">
+      <c r="N302" s="8" t="n">
         <v>15.9166311155573</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
@@ -24497,7 +24512,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -24530,7 +24545,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n">
+      <c r="N303" s="8" t="n">
         <v>10.0130859589153</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
@@ -24576,7 +24591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -24609,7 +24624,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n">
+      <c r="N304" s="8" t="n">
         <v>20.9626504331607</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
@@ -24655,7 +24670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24688,7 +24703,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n">
+      <c r="N305" s="8" t="n">
         <v>29.2548511239111</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
@@ -24734,7 +24749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24767,7 +24782,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n">
+      <c r="N306" s="8" t="n">
         <v>16.6639894189064</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
@@ -24813,7 +24828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24846,7 +24861,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n">
+      <c r="N307" s="8" t="n">
         <v>15.7571776112482</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
@@ -24892,7 +24907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24925,7 +24940,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n">
+      <c r="N308" s="8" t="n">
         <v>15.7932181812518</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
@@ -24971,7 +24986,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -25004,7 +25019,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n">
+      <c r="N309" s="8" t="n">
         <v>16.2198265911409</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
@@ -25050,7 +25065,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -25083,7 +25098,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n">
+      <c r="N310" s="8" t="n">
         <v>15.1363210095652</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
@@ -25129,7 +25144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -25162,7 +25177,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n">
+      <c r="N311" s="8" t="n">
         <v>23.8367720643582</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
@@ -25208,7 +25223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -25241,7 +25256,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n">
+      <c r="N312" s="8" t="n">
         <v>18.0963540802062</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
@@ -25287,7 +25302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -25320,7 +25335,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n">
+      <c r="N313" s="8" t="n">
         <v>9.06347009522954</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
@@ -25366,7 +25381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -25399,7 +25414,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n">
+      <c r="N314" s="8" t="n">
         <v>13.269532614572</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
@@ -25445,7 +25460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -25478,7 +25493,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n">
+      <c r="N315" s="8" t="n">
         <v>20.5761295010598</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
@@ -25524,7 +25539,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -25557,7 +25572,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n">
+      <c r="N316" s="8" t="n">
         <v>15.3442903568827</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
@@ -25603,7 +25618,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25636,7 +25651,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n">
+      <c r="N317" s="8" t="n">
         <v>19.4545884689745</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
@@ -25682,7 +25697,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25715,7 +25730,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n">
+      <c r="N318" s="8" t="n">
         <v>21.8955843439596</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
@@ -25761,7 +25776,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25794,7 +25809,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n">
+      <c r="N319" s="8" t="n">
         <v>23.8297115705399</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
@@ -25840,7 +25855,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25873,7 +25888,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n">
+      <c r="N320" s="8" t="n">
         <v>29.2230041014033</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
@@ -25919,7 +25934,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25952,7 +25967,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n">
+      <c r="N321" s="8" t="n">
         <v>28.0774680117788</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
@@ -25998,7 +26013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -26031,7 +26046,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n">
+      <c r="N322" s="8" t="n">
         <v>23.1186941835454</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
@@ -26077,7 +26092,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -26110,7 +26125,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n">
+      <c r="N323" s="8" t="n">
         <v>23.9223070628002</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
@@ -26156,7 +26171,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -26189,7 +26204,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n">
+      <c r="N324" s="8" t="n">
         <v>10.5416668243022</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
@@ -26235,7 +26250,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -26268,7 +26283,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n">
+      <c r="N325" s="8" t="n">
         <v>12.380878328857</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
@@ -26314,7 +26329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -26347,7 +26362,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n">
+      <c r="N326" s="8" t="n">
         <v>24.4753357613612</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
@@ -26393,7 +26408,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -26426,7 +26441,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n">
+      <c r="N327" s="8" t="n">
         <v>18.7812359044725</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
@@ -26472,7 +26487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -26505,7 +26520,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N328" s="4" t="n">
+      <c r="N328" s="8" t="n">
         <v>17.6253449138361</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
@@ -26551,7 +26566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -26584,7 +26599,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N329" s="4" t="n">
+      <c r="N329" s="8" t="n">
         <v>11.8465082797294</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
@@ -26630,7 +26645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -26707,7 +26722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26784,7 +26799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -26861,7 +26876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26938,7 +26953,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -27015,7 +27030,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -27092,7 +27107,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -27169,7 +27184,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -27246,7 +27261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -27323,7 +27338,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -27400,7 +27415,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n">
+      <c r="G340" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -27536,7 +27551,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -27546,7 +27561,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>334</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12399,7 +12399,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,14 +21309,10 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21390,14 +21386,10 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -21471,14 +21463,10 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q273" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -21552,14 +21540,10 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q274" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q274" s="4" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -21633,14 +21617,10 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q275" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -21714,14 +21694,10 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q276" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q276" s="4" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -21795,14 +21771,10 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q277" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -21876,14 +21848,10 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q278" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -21957,14 +21925,10 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q279" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -22038,14 +22002,10 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q280" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q280" s="4" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -22111,7 +22071,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N281" s="4" t="n"/>
+      <c r="N281" s="6" t="n">
+        <v>5.48772130601331</v>
+      </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22119,14 +22081,10 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q281" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -22192,7 +22150,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N282" s="4" t="n"/>
+      <c r="N282" s="6" t="n">
+        <v>7.38794104909662</v>
+      </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22200,14 +22160,10 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q282" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -22273,7 +22229,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N283" s="4" t="n"/>
+      <c r="N283" s="6" t="n">
+        <v>7.19271915747182</v>
+      </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22281,14 +22239,10 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q283" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -22354,7 +22308,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N284" s="4" t="n"/>
+      <c r="N284" s="6" t="n">
+        <v>10.7554427076038</v>
+      </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22362,14 +22318,10 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q284" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -22435,7 +22387,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N285" s="4" t="n"/>
+      <c r="N285" s="6" t="n">
+        <v>33.9478841729493</v>
+      </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22443,14 +22397,10 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q285" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -22516,7 +22466,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N286" s="4" t="n"/>
+      <c r="N286" s="6" t="n">
+        <v>24.8915014056924</v>
+      </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22524,14 +22476,10 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q286" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -22597,7 +22545,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N287" s="4" t="n"/>
+      <c r="N287" s="6" t="n">
+        <v>22.9931513860828</v>
+      </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22605,14 +22555,10 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q287" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -22678,7 +22624,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N288" s="4" t="n"/>
+      <c r="N288" s="6" t="n">
+        <v>16.1985343555775</v>
+      </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22686,14 +22634,10 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q288" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q288" s="4" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -22759,7 +22703,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N289" s="4" t="n"/>
+      <c r="N289" s="6" t="n">
+        <v>15.8263995123574</v>
+      </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22767,14 +22713,10 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q289" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -22840,7 +22782,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N290" s="4" t="n"/>
+      <c r="N290" s="6" t="n">
+        <v>36.481380981255</v>
+      </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22848,14 +22792,10 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q290" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -22921,7 +22861,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N291" s="4" t="n"/>
+      <c r="N291" s="6" t="n">
+        <v>34.4312946645093</v>
+      </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22929,14 +22871,10 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q291" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -23002,7 +22940,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N292" s="4" t="n"/>
+      <c r="N292" s="6" t="n">
+        <v>24.750858904318</v>
+      </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23010,14 +22950,10 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q292" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -23083,7 +23019,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N293" s="4" t="n"/>
+      <c r="N293" s="6" t="n">
+        <v>13.1086608763643</v>
+      </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23091,14 +23029,10 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q293" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -23164,7 +23098,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N294" s="4" t="n"/>
+      <c r="N294" s="6" t="n">
+        <v>17.0995109701258</v>
+      </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23172,14 +23108,10 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q294" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -23245,7 +23177,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N295" s="4" t="n"/>
+      <c r="N295" s="6" t="n">
+        <v>19.0260300794035</v>
+      </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23253,14 +23187,10 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q295" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -23326,7 +23256,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N296" s="4" t="n"/>
+      <c r="N296" s="6" t="n">
+        <v>16.3107385078032</v>
+      </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23334,14 +23266,10 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q296" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -23407,7 +23335,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N297" s="4" t="n"/>
+      <c r="N297" s="6" t="n">
+        <v>8.00102414924425</v>
+      </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23415,14 +23345,10 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q297" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -23488,7 +23414,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N298" s="4" t="n"/>
+      <c r="N298" s="6" t="n">
+        <v>15.9166311155573</v>
+      </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23496,14 +23424,10 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q298" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -23569,7 +23493,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N299" s="4" t="n"/>
+      <c r="N299" s="6" t="n">
+        <v>10.0130859589153</v>
+      </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23577,14 +23503,10 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q299" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -23650,7 +23572,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N300" s="4" t="n"/>
+      <c r="N300" s="6" t="n">
+        <v>20.9626504331607</v>
+      </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23658,14 +23582,10 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q300" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -23731,7 +23651,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N301" s="4" t="n"/>
+      <c r="N301" s="6" t="n">
+        <v>29.2548511239111</v>
+      </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23739,14 +23661,10 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q301" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -23812,7 +23730,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="6" t="n">
+        <v>16.6639894189064</v>
+      </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23820,14 +23740,10 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q302" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -23893,7 +23809,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n"/>
+      <c r="N303" s="6" t="n">
+        <v>15.7571776112482</v>
+      </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23901,14 +23819,10 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q303" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -23974,7 +23888,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n"/>
+      <c r="N304" s="6" t="n">
+        <v>15.7932181812518</v>
+      </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23982,14 +23898,10 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q304" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -24055,7 +23967,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n"/>
+      <c r="N305" s="6" t="n">
+        <v>16.2198265911409</v>
+      </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24063,14 +23977,10 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q305" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -24136,7 +24046,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n"/>
+      <c r="N306" s="6" t="n">
+        <v>15.1363210095652</v>
+      </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24144,14 +24056,10 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q306" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -24217,7 +24125,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n"/>
+      <c r="N307" s="6" t="n">
+        <v>23.8367720643582</v>
+      </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24225,14 +24135,10 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q307" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -24298,7 +24204,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n"/>
+      <c r="N308" s="6" t="n">
+        <v>18.0963540802062</v>
+      </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24306,14 +24214,10 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q308" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q308" s="4" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -24379,7 +24283,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n"/>
+      <c r="N309" s="6" t="n">
+        <v>9.06347009522954</v>
+      </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24387,14 +24293,10 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q309" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -24460,7 +24362,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n"/>
+      <c r="N310" s="6" t="n">
+        <v>13.269532614572</v>
+      </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24468,14 +24372,10 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q310" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -24541,7 +24441,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n"/>
+      <c r="N311" s="6" t="n">
+        <v>20.5761295010598</v>
+      </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24549,14 +24451,10 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q311" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -24622,7 +24520,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n"/>
+      <c r="N312" s="6" t="n">
+        <v>15.3442903568827</v>
+      </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24630,14 +24530,10 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q312" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -24703,7 +24599,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n"/>
+      <c r="N313" s="6" t="n">
+        <v>19.4545884689745</v>
+      </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24711,14 +24609,10 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q313" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -24784,7 +24678,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n"/>
+      <c r="N314" s="6" t="n">
+        <v>21.8955843439596</v>
+      </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24792,14 +24688,10 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q314" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -24865,7 +24757,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n"/>
+      <c r="N315" s="6" t="n">
+        <v>23.8297115705399</v>
+      </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24873,14 +24767,10 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q315" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -24946,7 +24836,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n"/>
+      <c r="N316" s="6" t="n">
+        <v>29.2230041014033</v>
+      </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24954,14 +24846,10 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q316" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -25027,7 +24915,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n"/>
+      <c r="N317" s="6" t="n">
+        <v>28.0774680117788</v>
+      </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25035,14 +24925,10 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q317" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -25108,7 +24994,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n"/>
+      <c r="N318" s="6" t="n">
+        <v>23.1186941835454</v>
+      </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25116,14 +25004,10 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q318" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -25189,7 +25073,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n"/>
+      <c r="N319" s="6" t="n">
+        <v>23.9223070628002</v>
+      </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25197,14 +25083,10 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q319" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -25270,7 +25152,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n"/>
+      <c r="N320" s="6" t="n">
+        <v>10.5416668243022</v>
+      </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25278,14 +25162,10 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q320" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -25351,7 +25231,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n"/>
+      <c r="N321" s="6" t="n">
+        <v>12.380878328857</v>
+      </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25359,14 +25241,10 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q321" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -25432,7 +25310,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n"/>
+      <c r="N322" s="6" t="n">
+        <v>24.4753357613612</v>
+      </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25440,14 +25320,10 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q322" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -25513,7 +25389,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n"/>
+      <c r="N323" s="6" t="n">
+        <v>18.7812359044725</v>
+      </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25521,14 +25399,10 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q323" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -25594,7 +25468,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n"/>
+      <c r="N324" s="6" t="n">
+        <v>17.6253449138361</v>
+      </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25602,14 +25478,10 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q324" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -25675,7 +25547,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n"/>
+      <c r="N325" s="6" t="n">
+        <v>11.8465082797294</v>
+      </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25683,14 +25557,10 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q325" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -25764,14 +25634,10 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q326" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -25845,14 +25711,10 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q327" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -25926,14 +25788,10 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q328" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -26007,14 +25865,10 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q329" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -26088,14 +25942,10 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q330" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -26169,14 +26019,10 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q331" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -26250,14 +26096,10 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q332" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -26331,14 +26173,10 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q333" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -26412,14 +26250,10 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q334" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -26493,14 +26327,10 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q335" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -26574,95 +26404,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Energía y ambiente</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>energia_y_ambiente</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Recursos naturales</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>recursos_naturales</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N337" s="4" t="n"/>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26744,7 +26489,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -26765,7 +26510,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q336"/>
+  <dimension ref="A1:Q337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,10 +715,14 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -792,10 +796,14 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -869,10 +877,14 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -946,10 +958,14 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1023,10 +1039,14 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1100,10 +1120,14 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1177,10 +1201,14 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1254,10 +1282,14 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1331,10 +1363,14 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1408,10 +1444,14 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1485,10 +1525,14 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1562,10 +1606,14 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1639,10 +1687,14 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1716,10 +1768,14 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1793,10 +1849,14 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1870,10 +1930,14 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1947,10 +2011,14 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2024,10 +2092,14 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2101,10 +2173,14 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2178,10 +2254,14 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2255,10 +2335,14 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2332,10 +2416,14 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2409,10 +2497,14 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2486,10 +2578,14 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2563,10 +2659,14 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2640,10 +2740,14 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2717,10 +2821,14 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2794,10 +2902,14 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2871,10 +2983,14 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2948,10 +3064,14 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3017,9 +3137,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N37" s="6" t="n">
-        <v>58.9830508474576</v>
-      </c>
+      <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3027,10 +3145,14 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3096,9 +3218,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>58.6571056062582</v>
-      </c>
+      <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3106,10 +3226,14 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3175,9 +3299,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
-        <v>58.3311603650587</v>
-      </c>
+      <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3185,10 +3307,14 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3254,9 +3380,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N40" s="6" t="n">
-        <v>58.0052151238592</v>
-      </c>
+      <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3264,10 +3388,14 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3333,9 +3461,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N41" s="6" t="n">
-        <v>57.6792698826597</v>
-      </c>
+      <c r="N41" s="4" t="n"/>
       <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3343,10 +3469,14 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3412,9 +3542,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>57.3533246414602</v>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3422,10 +3550,14 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3491,9 +3623,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N43" s="6" t="n">
-        <v>57.0273794002608</v>
-      </c>
+      <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3501,10 +3631,14 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3570,9 +3704,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N44" s="6" t="n">
-        <v>56.7014341590613</v>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3580,10 +3712,14 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3649,9 +3785,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
-        <v>56.3754889178618</v>
-      </c>
+      <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3659,10 +3793,14 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -3728,9 +3866,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>56.0495436766623</v>
-      </c>
+      <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3738,10 +3874,14 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3807,9 +3947,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N47" s="6" t="n">
-        <v>55.7235984354628</v>
-      </c>
+      <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3817,10 +3955,14 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -3886,9 +4028,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N48" s="6" t="n">
-        <v>55.53698769911</v>
-      </c>
+      <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3896,10 +4036,14 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -3965,9 +4109,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N49" s="6" t="n">
-        <v>55.3503769627572</v>
-      </c>
+      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3975,10 +4117,14 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4044,9 +4190,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N50" s="6" t="n">
-        <v>55.1637662264044</v>
-      </c>
+      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4054,10 +4198,14 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4123,9 +4271,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N51" s="6" t="n">
-        <v>54.9771554900516</v>
-      </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4133,10 +4279,14 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4202,9 +4352,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>54.7905447536988</v>
-      </c>
+      <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4212,10 +4360,14 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4281,9 +4433,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
-        <v>54.603934017346</v>
-      </c>
+      <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4291,10 +4441,14 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4360,9 +4514,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N54" s="6" t="n">
-        <v>54.4173232809931</v>
-      </c>
+      <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4370,10 +4522,14 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4439,9 +4595,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N55" s="6" t="n">
-        <v>54.2307125446403</v>
-      </c>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4449,10 +4603,14 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4518,9 +4676,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>54.0441018082875</v>
-      </c>
+      <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4528,10 +4684,14 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4597,9 +4757,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N57" s="6" t="n">
-        <v>53.8574910719347</v>
-      </c>
+      <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4607,10 +4765,14 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4676,9 +4838,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>53.6711070800975</v>
-      </c>
+      <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4686,10 +4846,14 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4755,9 +4919,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N59" s="6" t="n">
-        <v>53.4847230882603</v>
-      </c>
+      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4765,10 +4927,14 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -4834,9 +5000,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N60" s="6" t="n">
-        <v>53.2983390964231</v>
-      </c>
+      <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4844,10 +5008,14 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -4913,9 +5081,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N61" s="6" t="n">
-        <v>53.1119551045859</v>
-      </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4923,10 +5089,14 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -4992,9 +5162,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N62" s="6" t="n">
-        <v>52.9255711127487</v>
-      </c>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5002,10 +5170,14 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5071,9 +5243,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>52.7671447196871</v>
-      </c>
+      <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5081,10 +5251,14 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5150,9 +5324,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N64" s="6" t="n">
-        <v>52.6366759254011</v>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5160,10 +5332,14 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5229,9 +5405,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
-        <v>52.5341647298906</v>
-      </c>
+      <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5239,10 +5413,14 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5308,9 +5486,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N66" s="6" t="n">
-        <v>52.4596111331557</v>
-      </c>
+      <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5318,10 +5494,14 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q66" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5387,9 +5567,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
-        <v>52.4130151351964</v>
-      </c>
+      <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5397,10 +5575,14 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q67" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5466,9 +5648,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N68" s="6" t="n">
-        <v>52.3477807380534</v>
-      </c>
+      <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5476,10 +5656,14 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5545,9 +5729,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
-        <v>52.2949719403662</v>
-      </c>
+      <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5555,10 +5737,14 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5624,9 +5810,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
-        <v>52.2338793719177</v>
-      </c>
+      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5634,10 +5818,14 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5711,10 +5899,14 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q71" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5788,10 +5980,14 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5825,7 +6021,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -5839,22 +6035,22 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Bosques</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>electricidad</t>
+          <t>bosques</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.ACCS.ZS</t>
+          <t>AG.LND.FRST.ZS</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>Acceso a electricidad</t>
+          <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
       <c r="N73" s="4" t="n"/>
@@ -5865,10 +6061,14 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5902,7 +6102,7 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -5942,7 +6142,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +6179,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -6019,7 +6219,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6256,7 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -6096,7 +6296,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6333,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -6173,7 +6373,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6410,7 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -6250,7 +6450,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6487,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -6327,7 +6527,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6564,7 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -6404,7 +6604,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6641,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -6481,7 +6681,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6718,7 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -6558,7 +6758,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6795,7 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -6635,7 +6835,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6672,7 +6872,7 @@
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -6712,7 +6912,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6749,7 +6949,7 @@
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -6789,7 +6989,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6826,7 +7026,7 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -6866,7 +7066,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6903,7 +7103,7 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -6943,7 +7143,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6980,7 +7180,7 @@
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -7020,7 +7220,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7057,7 +7257,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -7097,7 +7297,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7134,7 +7334,7 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -7174,7 +7374,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7211,7 +7411,7 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -7251,7 +7451,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7288,7 +7488,7 @@
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7528,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7365,7 +7565,7 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -7405,7 +7605,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7642,7 @@
         </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
@@ -7482,7 +7682,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7719,7 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -7559,7 +7759,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7796,7 @@
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -7636,7 +7836,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7873,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -7713,7 +7913,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7950,7 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -7790,7 +7990,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +8027,7 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -7867,7 +8067,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7904,7 +8104,7 @@
         </is>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -7944,7 +8144,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7981,7 +8181,7 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -8021,7 +8221,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8058,7 +8258,7 @@
         </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -8098,7 +8298,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8135,7 +8335,7 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -8175,7 +8375,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8212,7 +8412,7 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -8252,7 +8452,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8289,7 +8489,7 @@
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -8321,9 +8521,7 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N105" s="6" t="n">
-        <v>97.82020300000001</v>
-      </c>
+      <c r="N105" s="4" t="n"/>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8331,7 +8529,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8368,7 +8566,7 @@
         </is>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -8401,7 +8599,7 @@
         </is>
       </c>
       <c r="N106" s="6" t="n">
-        <v>98.2395324707031</v>
+        <v>97.82020300000001</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
@@ -8410,7 +8608,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8447,7 +8645,7 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8480,7 +8678,7 @@
         </is>
       </c>
       <c r="N107" s="6" t="n">
-        <v>98.3233337402344</v>
+        <v>98.2395324707031</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
@@ -8489,7 +8687,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8526,7 +8724,7 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -8558,8 +8756,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N108" s="5" t="n">
-        <v>99</v>
+      <c r="N108" s="6" t="n">
+        <v>98.3233337402344</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
@@ -8568,7 +8766,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8803,7 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -8637,8 +8835,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N109" s="6" t="n">
-        <v>98.484130859375</v>
+      <c r="N109" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
@@ -8647,7 +8845,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8684,7 +8882,7 @@
         </is>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
@@ -8717,7 +8915,7 @@
         </is>
       </c>
       <c r="N110" s="6" t="n">
-        <v>98.7</v>
+        <v>98.484130859375</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
@@ -8726,7 +8924,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8763,7 +8961,7 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -8796,7 +8994,7 @@
         </is>
       </c>
       <c r="N111" s="6" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
@@ -8805,7 +9003,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8842,7 +9040,7 @@
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -8875,7 +9073,7 @@
         </is>
       </c>
       <c r="N112" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
@@ -8884,7 +9082,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8921,7 +9119,7 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -8963,7 +9161,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9000,7 +9198,7 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -9033,7 +9231,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
@@ -9042,7 +9240,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9079,7 +9277,7 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -9112,7 +9310,7 @@
         </is>
       </c>
       <c r="N115" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
@@ -9121,7 +9319,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9158,7 +9356,7 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -9191,7 +9389,7 @@
         </is>
       </c>
       <c r="N116" s="6" t="n">
-        <v>95.7</v>
+        <v>99.8</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
@@ -9200,7 +9398,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9237,7 +9435,7 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -9270,7 +9468,7 @@
         </is>
       </c>
       <c r="N117" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
@@ -9279,7 +9477,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9316,7 +9514,7 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -9349,7 +9547,7 @@
         </is>
       </c>
       <c r="N118" s="6" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
@@ -9358,7 +9556,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9395,7 +9593,7 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -9428,7 +9626,7 @@
         </is>
       </c>
       <c r="N119" s="6" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
@@ -9437,7 +9635,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9474,7 +9672,7 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -9507,7 +9705,7 @@
         </is>
       </c>
       <c r="N120" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -9516,7 +9714,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9553,7 +9751,7 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -9595,7 +9793,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9632,7 +9830,7 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
@@ -9664,8 +9862,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N122" s="5" t="n">
-        <v>99</v>
+      <c r="N122" s="6" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
@@ -9674,7 +9872,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9711,7 +9909,7 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -9743,8 +9941,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N123" s="6" t="n">
-        <v>99.09999999999999</v>
+      <c r="N123" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
@@ -9753,7 +9951,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9790,7 +9988,7 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
@@ -9823,7 +10021,7 @@
         </is>
       </c>
       <c r="N124" s="6" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
@@ -9832,7 +10030,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9869,7 +10067,7 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -9902,7 +10100,7 @@
         </is>
       </c>
       <c r="N125" s="6" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
@@ -9911,7 +10109,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9948,7 +10146,7 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
@@ -9981,7 +10179,7 @@
         </is>
       </c>
       <c r="N126" s="6" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
@@ -9990,7 +10188,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10027,7 +10225,7 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -10059,8 +10257,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N127" s="5" t="n">
-        <v>100</v>
+      <c r="N127" s="6" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
@@ -10069,7 +10267,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10106,7 +10304,7 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
@@ -10148,7 +10346,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10185,7 +10383,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -10217,8 +10415,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N129" s="6" t="n">
-        <v>99.40000000000001</v>
+      <c r="N129" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
@@ -10227,7 +10425,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10264,7 +10462,7 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
@@ -10297,7 +10495,7 @@
         </is>
       </c>
       <c r="N130" s="6" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
@@ -10306,7 +10504,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10343,7 +10541,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -10376,7 +10574,7 @@
         </is>
       </c>
       <c r="N131" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
@@ -10385,7 +10583,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10422,7 +10620,7 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
@@ -10455,7 +10653,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
@@ -10464,7 +10662,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10501,7 +10699,7 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -10534,7 +10732,7 @@
         </is>
       </c>
       <c r="N133" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
@@ -10543,7 +10741,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10580,7 +10778,7 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
@@ -10612,8 +10810,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N134" s="5" t="n">
-        <v>100</v>
+      <c r="N134" s="6" t="n">
+        <v>99.90000000000001</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
@@ -10622,7 +10820,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10659,7 +10857,7 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -10701,7 +10899,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10738,7 +10936,7 @@
         </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
@@ -10780,7 +10978,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10817,7 +11015,7 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -10859,7 +11057,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10896,7 +11094,7 @@
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -10928,7 +11126,9 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N138" s="4" t="n"/>
+      <c r="N138" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10936,7 +11136,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10973,7 +11173,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -10997,12 +11197,12 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.RNEW.ZS</t>
+          <t>EG.ELC.ACCS.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
+          <t>Acceso a electricidad</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11013,7 +11213,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11050,7 +11250,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11090,7 +11290,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11127,7 +11327,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11167,7 +11367,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11204,7 +11404,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11244,7 +11444,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11281,7 +11481,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11321,7 +11521,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11358,7 +11558,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11398,7 +11598,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11435,7 +11635,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11475,7 +11675,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11512,7 +11712,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11552,7 +11752,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11589,7 +11789,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11629,7 +11829,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11666,7 +11866,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11706,7 +11906,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11743,7 +11943,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11783,7 +11983,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11820,7 +12020,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -11860,7 +12060,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11897,7 +12097,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -11937,7 +12137,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11974,7 +12174,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12014,7 +12214,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12051,7 +12251,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12091,7 +12291,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12128,7 +12328,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12168,7 +12368,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12205,7 +12405,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12245,7 +12445,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12282,7 +12482,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12322,7 +12522,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12359,7 +12559,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12399,7 +12599,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12436,7 +12636,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12476,7 +12676,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12513,7 +12713,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12553,7 +12753,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12590,7 +12790,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12630,7 +12830,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12667,7 +12867,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12707,7 +12907,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12744,7 +12944,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12784,7 +12984,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12821,7 +13021,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -12861,7 +13061,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12898,7 +13098,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -12938,7 +13138,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12975,7 +13175,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13015,7 +13215,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13052,7 +13252,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13092,7 +13292,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13129,7 +13329,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13169,7 +13369,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13206,7 +13406,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13246,7 +13446,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13283,7 +13483,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13315,9 +13515,7 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N169" s="6" t="n">
-        <v>62.3438579929536</v>
-      </c>
+      <c r="N169" s="4" t="n"/>
       <c r="O169" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13325,7 +13523,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13362,7 +13560,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13395,7 +13593,7 @@
         </is>
       </c>
       <c r="N170" s="6" t="n">
-        <v>70.3254022135561</v>
+        <v>62.3438579929536</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
@@ -13404,7 +13602,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13441,7 +13639,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13474,7 +13672,7 @@
         </is>
       </c>
       <c r="N171" s="6" t="n">
-        <v>70.09341637010679</v>
+        <v>70.3254022135561</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
@@ -13483,7 +13681,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13520,7 +13718,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13553,7 +13751,7 @@
         </is>
       </c>
       <c r="N172" s="6" t="n">
-        <v>68.42985212302899</v>
+        <v>70.09341637010679</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
@@ -13562,7 +13760,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13599,7 +13797,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13632,7 +13830,7 @@
         </is>
       </c>
       <c r="N173" s="6" t="n">
-        <v>72.0068519116553</v>
+        <v>68.42985212302899</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
@@ -13641,7 +13839,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13678,7 +13876,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13711,7 +13909,7 @@
         </is>
       </c>
       <c r="N174" s="6" t="n">
-        <v>70.0514663834654</v>
+        <v>72.0068519116553</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
@@ -13720,7 +13918,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13757,7 +13955,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13790,7 +13988,7 @@
         </is>
       </c>
       <c r="N175" s="6" t="n">
-        <v>71.237498015558</v>
+        <v>70.0514663834654</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
@@ -13799,7 +13997,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13836,7 +14034,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -13869,7 +14067,7 @@
         </is>
       </c>
       <c r="N176" s="6" t="n">
-        <v>73.359380003843</v>
+        <v>71.237498015558</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
@@ -13878,7 +14076,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13915,7 +14113,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -13948,7 +14146,7 @@
         </is>
       </c>
       <c r="N177" s="6" t="n">
-        <v>71.59649946849279</v>
+        <v>73.359380003843</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
@@ -13957,7 +14155,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13994,7 +14192,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14027,7 +14225,7 @@
         </is>
       </c>
       <c r="N178" s="6" t="n">
-        <v>75.1646552472619</v>
+        <v>71.59649946849279</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14036,7 +14234,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14073,7 +14271,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14106,7 +14304,7 @@
         </is>
       </c>
       <c r="N179" s="6" t="n">
-        <v>73.7484021531353</v>
+        <v>75.1646552472619</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
@@ -14115,7 +14313,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14152,7 +14350,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14185,7 +14383,7 @@
         </is>
       </c>
       <c r="N180" s="6" t="n">
-        <v>67.0679878826884</v>
+        <v>73.7484021531353</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
@@ -14194,7 +14392,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14231,7 +14429,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14264,7 +14462,7 @@
         </is>
       </c>
       <c r="N181" s="6" t="n">
-        <v>64.8151373949397</v>
+        <v>67.0679878826884</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
@@ -14273,7 +14471,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14310,7 +14508,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14343,7 +14541,7 @@
         </is>
       </c>
       <c r="N182" s="6" t="n">
-        <v>65.83572609414431</v>
+        <v>64.8151373949397</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
@@ -14352,7 +14550,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14389,7 +14587,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14422,7 +14620,7 @@
         </is>
       </c>
       <c r="N183" s="6" t="n">
-        <v>70.94119195375541</v>
+        <v>65.83572609414431</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
@@ -14431,7 +14629,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14468,7 +14666,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14501,7 +14699,7 @@
         </is>
       </c>
       <c r="N184" s="6" t="n">
-        <v>73.28606809382831</v>
+        <v>70.94119195375541</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14510,7 +14708,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14547,7 +14745,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14580,7 +14778,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>73.9008893155349</v>
+        <v>73.28606809382831</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14589,7 +14787,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14626,7 +14824,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14659,7 +14857,7 @@
         </is>
       </c>
       <c r="N186" s="6" t="n">
-        <v>72.7246397114189</v>
+        <v>73.9008893155349</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14668,7 +14866,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14705,7 +14903,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14738,7 +14936,7 @@
         </is>
       </c>
       <c r="N187" s="6" t="n">
-        <v>72.7965497875051</v>
+        <v>72.7246397114189</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
@@ -14747,7 +14945,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14784,7 +14982,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -14817,7 +15015,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>71.6609231333517</v>
+        <v>72.7965497875051</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -14826,7 +15024,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14863,7 +15061,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -14896,7 +15094,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>67.242625937084</v>
+        <v>71.6609231333517</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -14905,7 +15103,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14942,7 +15140,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -14975,7 +15173,7 @@
         </is>
       </c>
       <c r="N190" s="6" t="n">
-        <v>70.7004672541846</v>
+        <v>67.242625937084</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -14984,7 +15182,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15021,7 +15219,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15054,7 +15252,7 @@
         </is>
       </c>
       <c r="N191" s="6" t="n">
-        <v>67.0600784236679</v>
+        <v>70.7004672541846</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
@@ -15063,7 +15261,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15100,7 +15298,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15133,7 +15331,7 @@
         </is>
       </c>
       <c r="N192" s="6" t="n">
-        <v>65.96440553278519</v>
+        <v>67.0600784236679</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -15142,7 +15340,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15179,7 +15377,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15212,7 +15410,7 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>77.5369122989602</v>
+        <v>65.96440553278519</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
@@ -15221,7 +15419,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15258,7 +15456,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15291,7 +15489,7 @@
         </is>
       </c>
       <c r="N194" s="6" t="n">
-        <v>65.53966478494149</v>
+        <v>77.5369122989602</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
@@ -15300,7 +15498,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15337,7 +15535,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15370,7 +15568,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>62.32403609516</v>
+        <v>65.53966478494149</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15379,7 +15577,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15416,7 +15614,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15449,7 +15647,7 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>51.4746640846626</v>
+        <v>62.32403609516</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15458,7 +15656,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15495,7 +15693,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15528,7 +15726,7 @@
         </is>
       </c>
       <c r="N197" s="6" t="n">
-        <v>63.2932794208759</v>
+        <v>51.4746640846626</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
@@ -15537,7 +15735,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15574,7 +15772,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15607,7 +15805,7 @@
         </is>
       </c>
       <c r="N198" s="6" t="n">
-        <v>65.9218035546249</v>
+        <v>63.2932794208759</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -15616,7 +15814,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15653,7 +15851,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15686,7 +15884,7 @@
         </is>
       </c>
       <c r="N199" s="6" t="n">
-        <v>84.45121523562889</v>
+        <v>65.9218035546249</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
@@ -15695,7 +15893,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15732,7 +15930,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15765,7 +15963,7 @@
         </is>
       </c>
       <c r="N200" s="6" t="n">
-        <v>81.72207575243419</v>
+        <v>84.45121523562889</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
@@ -15774,7 +15972,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15811,7 +16009,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -15843,7 +16041,9 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n"/>
+      <c r="N201" s="6" t="n">
+        <v>81.72207575243419</v>
+      </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15851,7 +16051,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15888,7 +16088,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -15928,7 +16128,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15965,7 +16165,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16005,7 +16205,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16042,7 +16242,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16082,7 +16282,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16119,7 +16319,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16133,22 +16333,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16159,7 +16359,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16196,7 +16396,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16236,7 +16436,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16273,7 +16473,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16313,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16350,7 +16550,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16390,7 +16590,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16427,7 +16627,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16467,7 +16667,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16504,7 +16704,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16544,7 +16744,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16581,7 +16781,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16621,7 +16821,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16658,7 +16858,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16698,7 +16898,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16735,7 +16935,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16775,7 +16975,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16812,7 +17012,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -16852,7 +17052,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16889,7 +17089,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -16929,7 +17129,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16966,7 +17166,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17006,7 +17206,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17043,7 +17243,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17083,7 +17283,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17120,7 +17320,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17160,7 +17360,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17197,7 +17397,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17237,7 +17437,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17274,7 +17474,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17314,7 +17514,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17351,7 +17551,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17391,7 +17591,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17428,7 +17628,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17468,7 +17668,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17505,7 +17705,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17545,7 +17745,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17582,7 +17782,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17622,7 +17822,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17659,7 +17859,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17699,7 +17899,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17736,7 +17936,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17776,7 +17976,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17813,7 +18013,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -17853,7 +18053,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17890,7 +18090,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -17930,7 +18130,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17967,7 +18167,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18007,7 +18207,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18044,7 +18244,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18084,7 +18284,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18121,7 +18321,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18161,7 +18361,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18198,7 +18398,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18238,7 +18438,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18275,7 +18475,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18315,7 +18515,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18352,7 +18552,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18392,7 +18592,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18429,7 +18629,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18461,9 +18661,7 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N235" s="6" t="n">
-        <v>1997.56479057799</v>
-      </c>
+      <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18471,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18508,7 +18706,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18541,7 +18739,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>2037.30182520885</v>
+        <v>1997.56479057799</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18550,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18587,7 +18785,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18620,7 +18818,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>2226.55481105961</v>
+        <v>2037.30182520885</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18629,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18666,7 +18864,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18699,7 +18897,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>2027.59967205093</v>
+        <v>2226.55481105961</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18708,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18745,7 +18943,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18778,7 +18976,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>2299.11785137022</v>
+        <v>2027.59967205093</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18787,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18824,7 +19022,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -18857,7 +19055,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>2111.33770063193</v>
+        <v>2299.11785137022</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -18866,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18903,7 +19101,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -18936,7 +19134,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>2203.62644762536</v>
+        <v>2111.33770063193</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -18945,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18982,7 +19180,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19015,7 +19213,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>2149.90770739915</v>
+        <v>2203.62644762536</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19024,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19061,7 +19259,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19094,7 +19292,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>2218.43187719732</v>
+        <v>2149.90770739915</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19103,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19140,7 +19338,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19173,7 +19371,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>2399.16210710328</v>
+        <v>2218.43187719732</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19182,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19219,7 +19417,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19252,7 +19450,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>2391.36796026802</v>
+        <v>2399.16210710328</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19261,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19298,7 +19496,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19331,7 +19529,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>2188.40606705914</v>
+        <v>2391.36796026802</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19340,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19377,7 +19575,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19410,7 +19608,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>2648.88652521803</v>
+        <v>2188.40606705914</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19419,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19456,7 +19654,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19489,7 +19687,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>2432.12630470112</v>
+        <v>2648.88652521803</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19498,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19535,7 +19733,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19568,7 +19766,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>2305.02805179379</v>
+        <v>2432.12630470112</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19577,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19614,7 +19812,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19647,7 +19845,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>2371.58340737061</v>
+        <v>2305.02805179379</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19656,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19693,7 +19891,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19726,7 +19924,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>2377.64028480756</v>
+        <v>2371.58340737061</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19735,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19772,7 +19970,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -19805,7 +20003,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>2391.33788149518</v>
+        <v>2377.64028480756</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -19814,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19851,7 +20049,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -19884,7 +20082,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>2346.01163837283</v>
+        <v>2391.33788149518</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -19893,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19930,7 +20128,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -19963,7 +20161,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>2231.75458660546</v>
+        <v>2346.01163837283</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -19972,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20009,7 +20207,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20042,7 +20240,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>2621.20702328211</v>
+        <v>2231.75458660546</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20051,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20088,7 +20286,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20121,7 +20319,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>2309.9066118944</v>
+        <v>2621.20702328211</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20130,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20167,7 +20365,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20200,7 +20398,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>2310.75269478151</v>
+        <v>2309.9066118944</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20209,7 +20407,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20246,7 +20444,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20279,7 +20477,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>2529.2097489945</v>
+        <v>2310.75269478151</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20288,7 +20486,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20325,7 +20523,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20358,7 +20556,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>2173.57093050952</v>
+        <v>2529.2097489945</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20367,7 +20565,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20404,7 +20602,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20437,7 +20635,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>2098.46944015591</v>
+        <v>2173.57093050952</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20446,7 +20644,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20483,7 +20681,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20516,7 +20714,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>2009.0681450604</v>
+        <v>2098.46944015591</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20525,7 +20723,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20562,7 +20760,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20595,7 +20793,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>1933.19114696252</v>
+        <v>2009.0681450604</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20604,7 +20802,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20641,7 +20839,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20674,7 +20872,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>1451.3949056587</v>
+        <v>1933.19114696252</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20683,7 +20881,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20720,7 +20918,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20753,7 +20951,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>1379.73439965</v>
+        <v>1451.3949056587</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20762,7 +20960,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20799,7 +20997,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -20832,7 +21030,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>1093.43160664363</v>
+        <v>1379.73439965</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -20841,7 +21039,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20878,7 +21076,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -20911,7 +21109,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>1409.82623845927</v>
+        <v>1093.43160664363</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -20920,7 +21118,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20957,7 +21155,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -20990,7 +21188,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>1364.68351163595</v>
+        <v>1409.82623845927</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -20999,7 +21197,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21036,7 +21234,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21069,7 +21267,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>1331.23284099658</v>
+        <v>1364.68351163595</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21078,7 +21276,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21115,7 +21313,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21147,7 +21345,9 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n"/>
+      <c r="N269" s="6" t="n">
+        <v>1331.23284099658</v>
+      </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21155,7 +21355,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21192,7 +21392,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21232,7 +21432,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21269,7 +21469,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21283,22 +21483,22 @@
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>Recursos naturales</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>recursos_naturales</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21309,7 +21509,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21346,7 +21546,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21386,7 +21586,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21423,7 +21623,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21463,7 +21663,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21500,7 +21700,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21540,7 +21740,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21577,7 +21777,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21617,7 +21817,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21654,7 +21854,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21694,7 +21894,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21731,7 +21931,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21771,7 +21971,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21808,7 +22008,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -21848,7 +22048,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21885,7 +22085,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -21925,7 +22125,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21962,7 +22162,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22002,7 +22202,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22039,7 +22239,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22071,9 +22271,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N281" s="6" t="n">
-        <v>5.48772130601331</v>
-      </c>
+      <c r="N281" s="4" t="n"/>
       <c r="O281" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22081,7 +22279,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22118,7 +22316,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22151,7 +22349,7 @@
         </is>
       </c>
       <c r="N282" s="6" t="n">
-        <v>7.38794104909662</v>
+        <v>5.48772130601331</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
@@ -22160,7 +22358,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22197,7 +22395,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22230,7 +22428,7 @@
         </is>
       </c>
       <c r="N283" s="6" t="n">
-        <v>7.19271915747182</v>
+        <v>7.38794104909662</v>
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
@@ -22239,7 +22437,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22276,7 +22474,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22309,7 +22507,7 @@
         </is>
       </c>
       <c r="N284" s="6" t="n">
-        <v>10.7554427076038</v>
+        <v>7.19271915747182</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
@@ -22318,7 +22516,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22355,7 +22553,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22388,7 +22586,7 @@
         </is>
       </c>
       <c r="N285" s="6" t="n">
-        <v>33.9478841729493</v>
+        <v>10.7554427076038</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
@@ -22397,7 +22595,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22434,7 +22632,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22467,7 +22665,7 @@
         </is>
       </c>
       <c r="N286" s="6" t="n">
-        <v>24.8915014056924</v>
+        <v>33.9478841729493</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
@@ -22476,7 +22674,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22513,7 +22711,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22546,7 +22744,7 @@
         </is>
       </c>
       <c r="N287" s="6" t="n">
-        <v>22.9931513860828</v>
+        <v>24.8915014056924</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
@@ -22555,7 +22753,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22592,7 +22790,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22625,7 +22823,7 @@
         </is>
       </c>
       <c r="N288" s="6" t="n">
-        <v>16.1985343555775</v>
+        <v>22.9931513860828</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
@@ -22634,7 +22832,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22671,7 +22869,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22704,7 +22902,7 @@
         </is>
       </c>
       <c r="N289" s="6" t="n">
-        <v>15.8263995123574</v>
+        <v>16.1985343555775</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
@@ -22713,7 +22911,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22750,7 +22948,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22783,7 +22981,7 @@
         </is>
       </c>
       <c r="N290" s="6" t="n">
-        <v>36.481380981255</v>
+        <v>15.8263995123574</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
@@ -22792,7 +22990,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22829,7 +23027,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -22862,7 +23060,7 @@
         </is>
       </c>
       <c r="N291" s="6" t="n">
-        <v>34.4312946645093</v>
+        <v>36.481380981255</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
@@ -22871,7 +23069,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +23106,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -22941,7 +23139,7 @@
         </is>
       </c>
       <c r="N292" s="6" t="n">
-        <v>24.750858904318</v>
+        <v>34.4312946645093</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
@@ -22950,7 +23148,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22987,7 +23185,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23020,7 +23218,7 @@
         </is>
       </c>
       <c r="N293" s="6" t="n">
-        <v>13.1086608763643</v>
+        <v>24.750858904318</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
@@ -23029,7 +23227,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23066,7 +23264,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23099,7 +23297,7 @@
         </is>
       </c>
       <c r="N294" s="6" t="n">
-        <v>17.0995109701258</v>
+        <v>13.1086608763643</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
@@ -23108,7 +23306,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23145,7 +23343,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23178,7 +23376,7 @@
         </is>
       </c>
       <c r="N295" s="6" t="n">
-        <v>19.0260300794035</v>
+        <v>17.0995109701258</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
@@ -23187,7 +23385,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23224,7 +23422,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23257,7 +23455,7 @@
         </is>
       </c>
       <c r="N296" s="6" t="n">
-        <v>16.3107385078032</v>
+        <v>19.0260300794035</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
@@ -23266,7 +23464,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23303,7 +23501,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23336,7 +23534,7 @@
         </is>
       </c>
       <c r="N297" s="6" t="n">
-        <v>8.00102414924425</v>
+        <v>16.3107385078032</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
@@ -23345,7 +23543,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23382,7 +23580,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23415,7 +23613,7 @@
         </is>
       </c>
       <c r="N298" s="6" t="n">
-        <v>15.9166311155573</v>
+        <v>8.00102414924425</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
@@ -23424,7 +23622,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23461,7 +23659,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23494,7 +23692,7 @@
         </is>
       </c>
       <c r="N299" s="6" t="n">
-        <v>10.0130859589153</v>
+        <v>15.9166311155573</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
@@ -23503,7 +23701,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23540,7 +23738,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23573,7 +23771,7 @@
         </is>
       </c>
       <c r="N300" s="6" t="n">
-        <v>20.9626504331607</v>
+        <v>10.0130859589153</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
@@ -23582,7 +23780,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23619,7 +23817,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23652,7 +23850,7 @@
         </is>
       </c>
       <c r="N301" s="6" t="n">
-        <v>29.2548511239111</v>
+        <v>20.9626504331607</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
@@ -23661,7 +23859,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23698,7 +23896,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23731,7 +23929,7 @@
         </is>
       </c>
       <c r="N302" s="6" t="n">
-        <v>16.6639894189064</v>
+        <v>29.2548511239111</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
@@ -23740,7 +23938,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23777,7 +23975,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23810,7 +24008,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>15.7571776112482</v>
+        <v>16.6639894189064</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -23819,7 +24017,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23856,7 +24054,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -23889,7 +24087,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>15.7932181812518</v>
+        <v>15.7571776112482</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -23898,7 +24096,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23935,7 +24133,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -23968,7 +24166,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>16.2198265911409</v>
+        <v>15.7932181812518</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -23977,7 +24175,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24014,7 +24212,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24047,7 +24245,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>15.1363210095652</v>
+        <v>16.2198265911409</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24056,7 +24254,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24093,7 +24291,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24126,7 +24324,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>23.8367720643582</v>
+        <v>15.1363210095652</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24135,7 +24333,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24172,7 +24370,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24205,7 +24403,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>18.0963540802062</v>
+        <v>23.8367720643582</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24214,7 +24412,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24251,7 +24449,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24284,7 +24482,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>9.06347009522954</v>
+        <v>18.0963540802062</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24293,7 +24491,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24330,7 +24528,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24363,7 +24561,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>13.269532614572</v>
+        <v>9.06347009522954</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24372,7 +24570,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24409,7 +24607,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24442,7 +24640,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>20.5761295010598</v>
+        <v>13.269532614572</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24451,7 +24649,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24488,7 +24686,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24521,7 +24719,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>15.3442903568827</v>
+        <v>20.5761295010598</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24530,7 +24728,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24567,7 +24765,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24600,7 +24798,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>19.4545884689745</v>
+        <v>15.3442903568827</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24609,7 +24807,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24646,7 +24844,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24679,7 +24877,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>21.8955843439596</v>
+        <v>19.4545884689745</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24688,7 +24886,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24923,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24758,7 +24956,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>23.8297115705399</v>
+        <v>21.8955843439596</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24767,7 +24965,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24804,7 +25002,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24837,7 +25035,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>29.2230041014033</v>
+        <v>23.8297115705399</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -24846,7 +25044,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24883,7 +25081,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -24916,7 +25114,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>28.0774680117788</v>
+        <v>29.2230041014033</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -24925,7 +25123,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24962,7 +25160,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -24995,7 +25193,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>23.1186941835454</v>
+        <v>28.0774680117788</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25004,7 +25202,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25041,7 +25239,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25074,7 +25272,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>23.9223070628002</v>
+        <v>23.1186941835454</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25083,7 +25281,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25120,7 +25318,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25153,7 +25351,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>10.5416668243022</v>
+        <v>23.9223070628002</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25162,7 +25360,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25397,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25232,7 +25430,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>12.380878328857</v>
+        <v>10.5416668243022</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25241,7 +25439,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25278,7 +25476,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25311,7 +25509,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>24.4753357613612</v>
+        <v>12.380878328857</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25320,7 +25518,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25357,7 +25555,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25390,7 +25588,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>18.7812359044725</v>
+        <v>24.4753357613612</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25399,7 +25597,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25436,7 +25634,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25469,7 +25667,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>17.6253449138361</v>
+        <v>18.7812359044725</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25478,7 +25676,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25713,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25548,7 +25746,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>11.8465082797294</v>
+        <v>17.6253449138361</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25557,7 +25755,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25594,7 +25792,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25626,7 +25824,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="6" t="n">
+        <v>11.8465082797294</v>
+      </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25634,7 +25834,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25671,7 +25871,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25711,7 +25911,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25948,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25788,7 +25988,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +26025,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -25865,7 +26065,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +26102,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -25942,7 +26142,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +26179,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26019,7 +26219,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26256,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26096,7 +26296,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26333,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26173,7 +26373,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26410,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26250,7 +26450,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26487,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26327,7 +26527,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26564,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26404,10 +26604,87 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>Recursos naturales</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>recursos_naturales</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>NY.GDP.TOTL.RT.ZS</t>
+        </is>
+      </c>
+      <c r="M337" s="4" t="inlineStr">
+        <is>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="N337" s="4" t="n"/>
+      <c r="O337" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P337" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26489,7 +26766,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -26510,7 +26787,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,14 +715,10 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -796,14 +792,10 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -877,14 +869,10 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -958,14 +946,10 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1039,14 +1023,10 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1120,14 +1100,10 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1201,14 +1177,10 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1282,14 +1254,10 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1363,14 +1331,10 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1444,14 +1408,10 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1525,14 +1485,10 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1606,14 +1562,10 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1687,14 +1639,10 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1768,14 +1716,10 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1849,14 +1793,10 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1930,14 +1870,10 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2011,14 +1947,10 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2092,14 +2024,10 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2173,14 +2101,10 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2254,14 +2178,10 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2335,14 +2255,10 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2416,14 +2332,10 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2497,14 +2409,10 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2578,14 +2486,10 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2659,14 +2563,10 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2740,14 +2640,10 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2821,14 +2717,10 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2902,14 +2794,10 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2983,14 +2871,10 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3064,14 +2948,10 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3137,7 +3017,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n"/>
+      <c r="N37" s="6" t="n">
+        <v>58.9830508474576</v>
+      </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3145,14 +3027,10 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3218,7 +3096,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n"/>
+      <c r="N38" s="6" t="n">
+        <v>58.6571056062582</v>
+      </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3226,14 +3106,10 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3299,7 +3175,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n"/>
+      <c r="N39" s="6" t="n">
+        <v>58.3311603650587</v>
+      </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3307,14 +3185,10 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3380,7 +3254,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="6" t="n">
+        <v>58.0052151238592</v>
+      </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3388,14 +3264,10 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3461,7 +3333,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n"/>
+      <c r="N41" s="6" t="n">
+        <v>57.6792698826597</v>
+      </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3469,14 +3343,10 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3542,7 +3412,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="6" t="n">
+        <v>57.3533246414602</v>
+      </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3550,14 +3422,10 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3623,7 +3491,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n"/>
+      <c r="N43" s="6" t="n">
+        <v>57.0273794002608</v>
+      </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3631,14 +3501,10 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3704,7 +3570,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="6" t="n">
+        <v>56.7014341590613</v>
+      </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3712,14 +3580,10 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3785,7 +3649,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n"/>
+      <c r="N45" s="6" t="n">
+        <v>56.3754889178618</v>
+      </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3793,14 +3659,10 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -3866,7 +3728,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n"/>
+      <c r="N46" s="6" t="n">
+        <v>56.0495436766623</v>
+      </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3874,14 +3738,10 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3947,7 +3807,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n"/>
+      <c r="N47" s="6" t="n">
+        <v>55.7235984354628</v>
+      </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3955,14 +3817,10 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4028,7 +3886,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n"/>
+      <c r="N48" s="6" t="n">
+        <v>55.53698769911</v>
+      </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4036,14 +3896,10 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4109,7 +3965,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n"/>
+      <c r="N49" s="6" t="n">
+        <v>55.3503769627572</v>
+      </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4117,14 +3975,10 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4190,7 +4044,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n"/>
+      <c r="N50" s="6" t="n">
+        <v>55.1637662264044</v>
+      </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4198,14 +4054,10 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4271,7 +4123,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="6" t="n">
+        <v>54.9771554900516</v>
+      </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4279,14 +4133,10 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4352,7 +4202,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n"/>
+      <c r="N52" s="6" t="n">
+        <v>54.7905447536988</v>
+      </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4360,14 +4212,10 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4433,7 +4281,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n"/>
+      <c r="N53" s="6" t="n">
+        <v>54.603934017346</v>
+      </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4441,14 +4291,10 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4514,7 +4360,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n"/>
+      <c r="N54" s="6" t="n">
+        <v>54.4173232809931</v>
+      </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4522,14 +4370,10 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4595,7 +4439,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="6" t="n">
+        <v>54.2307125446403</v>
+      </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4603,14 +4449,10 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4676,7 +4518,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n"/>
+      <c r="N56" s="6" t="n">
+        <v>54.0441018082875</v>
+      </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4684,14 +4528,10 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4757,7 +4597,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n"/>
+      <c r="N57" s="6" t="n">
+        <v>53.8574910719347</v>
+      </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4765,14 +4607,10 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4838,7 +4676,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n"/>
+      <c r="N58" s="6" t="n">
+        <v>53.6711070800975</v>
+      </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4846,14 +4686,10 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4919,7 +4755,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n"/>
+      <c r="N59" s="6" t="n">
+        <v>53.4847230882603</v>
+      </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4927,14 +4765,10 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -5000,7 +4834,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n"/>
+      <c r="N60" s="6" t="n">
+        <v>53.2983390964231</v>
+      </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5008,14 +4844,10 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -5081,7 +4913,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n"/>
+      <c r="N61" s="6" t="n">
+        <v>53.1119551045859</v>
+      </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5089,14 +4923,10 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -5162,7 +4992,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n"/>
+      <c r="N62" s="6" t="n">
+        <v>52.9255711127487</v>
+      </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5170,14 +5002,10 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5243,7 +5071,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n"/>
+      <c r="N63" s="6" t="n">
+        <v>52.7671447196871</v>
+      </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5251,14 +5081,10 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5324,7 +5150,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n"/>
+      <c r="N64" s="6" t="n">
+        <v>52.6366759254011</v>
+      </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5332,14 +5160,10 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5405,7 +5229,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n"/>
+      <c r="N65" s="6" t="n">
+        <v>52.5341647298906</v>
+      </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5413,14 +5239,10 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5486,7 +5308,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n"/>
+      <c r="N66" s="6" t="n">
+        <v>52.4596111331557</v>
+      </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5494,14 +5318,10 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q66" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5567,7 +5387,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n"/>
+      <c r="N67" s="6" t="n">
+        <v>52.4130151351964</v>
+      </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5575,14 +5397,10 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q67" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5648,7 +5466,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n"/>
+      <c r="N68" s="6" t="n">
+        <v>52.3477807380534</v>
+      </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5656,14 +5476,10 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5729,7 +5545,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n"/>
+      <c r="N69" s="6" t="n">
+        <v>52.2949719403662</v>
+      </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5737,14 +5555,10 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5810,7 +5624,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n"/>
+      <c r="N70" s="6" t="n">
+        <v>52.2338793719177</v>
+      </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5818,14 +5634,10 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5899,14 +5711,10 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q71" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5980,14 +5788,10 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -6021,7 +5825,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -6035,22 +5839,22 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Bosques</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>bosques</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>AG.LND.FRST.ZS</t>
+          <t>EG.ELC.ACCS.ZS</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>Superficie forestal como porcentaje del territorio</t>
+          <t>Acceso a electricidad</t>
         </is>
       </c>
       <c r="N73" s="4" t="n"/>
@@ -6061,14 +5865,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -6102,7 +5902,7 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -6142,7 +5942,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6179,7 +5979,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -6219,7 +6019,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6256,7 +6056,7 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -6296,7 +6096,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6333,7 +6133,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -6373,7 +6173,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6410,7 +6210,7 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -6450,7 +6250,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6487,7 +6287,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -6527,7 +6327,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6564,7 +6364,7 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -6604,7 +6404,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6641,7 +6441,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -6681,7 +6481,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6718,7 +6518,7 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -6758,7 +6558,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6795,7 +6595,7 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -6835,7 +6635,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6872,7 +6672,7 @@
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -6912,7 +6712,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6949,7 +6749,7 @@
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -6989,7 +6789,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -7026,7 +6826,7 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -7066,7 +6866,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7103,7 +6903,7 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -7143,7 +6943,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7180,7 +6980,7 @@
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -7220,7 +7020,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7257,7 +7057,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -7297,7 +7097,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7334,7 +7134,7 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -7374,7 +7174,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7411,7 +7211,7 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -7451,7 +7251,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7488,7 +7288,7 @@
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -7528,7 +7328,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7565,7 +7365,7 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -7605,7 +7405,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7642,7 +7442,7 @@
         </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
@@ -7682,7 +7482,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7719,7 +7519,7 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -7759,7 +7559,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7796,7 +7596,7 @@
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -7836,7 +7636,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7873,7 +7673,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -7913,7 +7713,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7950,7 +7750,7 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -7990,7 +7790,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -8027,7 +7827,7 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -8067,7 +7867,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8104,7 +7904,7 @@
         </is>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -8144,7 +7944,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8181,7 +7981,7 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -8221,7 +8021,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8258,7 +8058,7 @@
         </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -8298,7 +8098,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8335,7 +8135,7 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -8375,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8412,7 +8212,7 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -8452,7 +8252,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8489,7 +8289,7 @@
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -8521,7 +8321,9 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n"/>
+      <c r="N105" s="6" t="n">
+        <v>97.82020300000001</v>
+      </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8529,7 +8331,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8566,7 +8368,7 @@
         </is>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -8599,7 +8401,7 @@
         </is>
       </c>
       <c r="N106" s="6" t="n">
-        <v>97.82020300000001</v>
+        <v>98.2395324707031</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
@@ -8608,7 +8410,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8645,7 +8447,7 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8678,7 +8480,7 @@
         </is>
       </c>
       <c r="N107" s="6" t="n">
-        <v>98.2395324707031</v>
+        <v>98.3233337402344</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
@@ -8687,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8724,7 +8526,7 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -8756,8 +8558,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N108" s="6" t="n">
-        <v>98.3233337402344</v>
+      <c r="N108" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
@@ -8766,7 +8568,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8803,7 +8605,7 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -8835,8 +8637,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N109" s="5" t="n">
-        <v>99</v>
+      <c r="N109" s="6" t="n">
+        <v>98.484130859375</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
@@ -8845,7 +8647,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8882,7 +8684,7 @@
         </is>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
@@ -8915,7 +8717,7 @@
         </is>
       </c>
       <c r="N110" s="6" t="n">
-        <v>98.484130859375</v>
+        <v>98.7</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
@@ -8924,7 +8726,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8961,7 +8763,7 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -8994,7 +8796,7 @@
         </is>
       </c>
       <c r="N111" s="6" t="n">
-        <v>98.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
@@ -9003,7 +8805,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9040,7 +8842,7 @@
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -9073,7 +8875,7 @@
         </is>
       </c>
       <c r="N112" s="6" t="n">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
@@ -9082,7 +8884,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9119,7 +8921,7 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -9161,7 +8963,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9198,7 +9000,7 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9033,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
@@ -9240,7 +9042,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9277,7 +9079,7 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -9310,7 +9112,7 @@
         </is>
       </c>
       <c r="N115" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
@@ -9319,7 +9121,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9356,7 +9158,7 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -9389,7 +9191,7 @@
         </is>
       </c>
       <c r="N116" s="6" t="n">
-        <v>99.8</v>
+        <v>95.7</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
@@ -9398,7 +9200,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9435,7 +9237,7 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -9468,7 +9270,7 @@
         </is>
       </c>
       <c r="N117" s="6" t="n">
-        <v>95.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
@@ -9477,7 +9279,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9514,7 +9316,7 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -9547,7 +9349,7 @@
         </is>
       </c>
       <c r="N118" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
@@ -9556,7 +9358,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9593,7 +9395,7 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -9626,7 +9428,7 @@
         </is>
       </c>
       <c r="N119" s="6" t="n">
-        <v>98.8</v>
+        <v>99.3</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
@@ -9635,7 +9437,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9672,7 +9474,7 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -9705,7 +9507,7 @@
         </is>
       </c>
       <c r="N120" s="6" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -9714,7 +9516,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9751,7 +9553,7 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -9793,7 +9595,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9830,7 +9632,7 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
@@ -9862,8 +9664,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N122" s="6" t="n">
-        <v>98.90000000000001</v>
+      <c r="N122" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
@@ -9872,7 +9674,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9909,7 +9711,7 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -9941,8 +9743,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N123" s="5" t="n">
-        <v>99</v>
+      <c r="N123" s="6" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
@@ -9951,7 +9753,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9988,7 +9790,7 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
@@ -10021,7 +9823,7 @@
         </is>
       </c>
       <c r="N124" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
@@ -10030,7 +9832,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10067,7 +9869,7 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -10100,7 +9902,7 @@
         </is>
       </c>
       <c r="N125" s="6" t="n">
-        <v>98.8</v>
+        <v>99.3</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
@@ -10109,7 +9911,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10146,7 +9948,7 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
@@ -10179,7 +9981,7 @@
         </is>
       </c>
       <c r="N126" s="6" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
@@ -10188,7 +9990,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10225,7 +10027,7 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -10257,8 +10059,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N127" s="6" t="n">
-        <v>99.40000000000001</v>
+      <c r="N127" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
@@ -10267,7 +10069,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10304,7 +10106,7 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
@@ -10346,7 +10148,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10383,7 +10185,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -10415,8 +10217,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N129" s="5" t="n">
-        <v>100</v>
+      <c r="N129" s="6" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
@@ -10425,7 +10227,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10462,7 +10264,7 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
@@ -10495,7 +10297,7 @@
         </is>
       </c>
       <c r="N130" s="6" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
@@ -10504,7 +10306,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10541,7 +10343,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -10574,7 +10376,7 @@
         </is>
       </c>
       <c r="N131" s="6" t="n">
-        <v>99.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
@@ -10583,7 +10385,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10620,7 +10422,7 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
@@ -10653,7 +10455,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
@@ -10662,7 +10464,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10699,7 +10501,7 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -10732,7 +10534,7 @@
         </is>
       </c>
       <c r="N133" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
@@ -10741,7 +10543,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10778,7 +10580,7 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
@@ -10810,8 +10612,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N134" s="6" t="n">
-        <v>99.90000000000001</v>
+      <c r="N134" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
@@ -10820,7 +10622,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10857,7 +10659,7 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -10899,7 +10701,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10936,7 +10738,7 @@
         </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
@@ -10978,7 +10780,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -11015,7 +10817,7 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -11057,7 +10859,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11094,7 +10896,7 @@
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -11126,9 +10928,7 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N138" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="N138" s="4" t="n"/>
       <c r="O138" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11136,7 +10936,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11173,7 +10973,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11197,12 +10997,12 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.ACCS.ZS</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Acceso a electricidad</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11213,7 +11013,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11250,7 +11050,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11290,7 +11090,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11327,7 +11127,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11367,7 +11167,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11404,7 +11204,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11444,7 +11244,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11481,7 +11281,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11521,7 +11321,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11558,7 +11358,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11598,7 +11398,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11635,7 +11435,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11675,7 +11475,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11712,7 +11512,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11752,7 +11552,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11789,7 +11589,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11829,7 +11629,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11866,7 +11666,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11906,7 +11706,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11943,7 +11743,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11983,7 +11783,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12020,7 +11820,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -12060,7 +11860,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12097,7 +11897,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -12137,7 +11937,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12174,7 +11974,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12214,7 +12014,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12251,7 +12051,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12291,7 +12091,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12128,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12368,7 +12168,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12405,7 +12205,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12445,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12482,7 +12282,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12522,7 +12322,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12559,7 +12359,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12599,7 +12399,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12636,7 +12436,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12676,7 +12476,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12713,7 +12513,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12753,7 +12553,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12790,7 +12590,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12830,7 +12630,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12667,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12907,7 +12707,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12944,7 +12744,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12984,7 +12784,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13021,7 +12821,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -13061,7 +12861,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13098,7 +12898,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -13138,7 +12938,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13175,7 +12975,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13215,7 +13015,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13252,7 +13052,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13292,7 +13092,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13329,7 +13129,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13369,7 +13169,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13406,7 +13206,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13446,7 +13246,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13483,7 +13283,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13515,7 +13315,9 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N169" s="4" t="n"/>
+      <c r="N169" s="6" t="n">
+        <v>62.3438579929536</v>
+      </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13523,7 +13325,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13560,7 +13362,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13593,7 +13395,7 @@
         </is>
       </c>
       <c r="N170" s="6" t="n">
-        <v>62.3438579929536</v>
+        <v>70.3254022135561</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
@@ -13602,7 +13404,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13639,7 +13441,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13672,7 +13474,7 @@
         </is>
       </c>
       <c r="N171" s="6" t="n">
-        <v>70.3254022135561</v>
+        <v>70.09341637010679</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
@@ -13681,7 +13483,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13718,7 +13520,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13751,7 +13553,7 @@
         </is>
       </c>
       <c r="N172" s="6" t="n">
-        <v>70.09341637010679</v>
+        <v>68.42985212302899</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
@@ -13760,7 +13562,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13797,7 +13599,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13830,7 +13632,7 @@
         </is>
       </c>
       <c r="N173" s="6" t="n">
-        <v>68.42985212302899</v>
+        <v>72.0068519116553</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
@@ -13839,7 +13641,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13876,7 +13678,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13909,7 +13711,7 @@
         </is>
       </c>
       <c r="N174" s="6" t="n">
-        <v>72.0068519116553</v>
+        <v>70.0514663834654</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
@@ -13918,7 +13720,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13955,7 +13757,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13988,7 +13790,7 @@
         </is>
       </c>
       <c r="N175" s="6" t="n">
-        <v>70.0514663834654</v>
+        <v>71.237498015558</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
@@ -13997,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14034,7 +13836,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -14067,7 +13869,7 @@
         </is>
       </c>
       <c r="N176" s="6" t="n">
-        <v>71.237498015558</v>
+        <v>73.359380003843</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
@@ -14076,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14113,7 +13915,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -14146,7 +13948,7 @@
         </is>
       </c>
       <c r="N177" s="6" t="n">
-        <v>73.359380003843</v>
+        <v>71.59649946849279</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
@@ -14155,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14192,7 +13994,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14225,7 +14027,7 @@
         </is>
       </c>
       <c r="N178" s="6" t="n">
-        <v>71.59649946849279</v>
+        <v>75.1646552472619</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14234,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14271,7 +14073,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14304,7 +14106,7 @@
         </is>
       </c>
       <c r="N179" s="6" t="n">
-        <v>75.1646552472619</v>
+        <v>73.7484021531353</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
@@ -14313,7 +14115,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14350,7 +14152,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14383,7 +14185,7 @@
         </is>
       </c>
       <c r="N180" s="6" t="n">
-        <v>73.7484021531353</v>
+        <v>67.0679878826884</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
@@ -14392,7 +14194,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14429,7 +14231,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14462,7 +14264,7 @@
         </is>
       </c>
       <c r="N181" s="6" t="n">
-        <v>67.0679878826884</v>
+        <v>64.8151373949397</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
@@ -14471,7 +14273,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14508,7 +14310,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14541,7 +14343,7 @@
         </is>
       </c>
       <c r="N182" s="6" t="n">
-        <v>64.8151373949397</v>
+        <v>65.83572609414431</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
@@ -14550,7 +14352,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14587,7 +14389,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14620,7 +14422,7 @@
         </is>
       </c>
       <c r="N183" s="6" t="n">
-        <v>65.83572609414431</v>
+        <v>70.94119195375541</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
@@ -14629,7 +14431,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14666,7 +14468,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14699,7 +14501,7 @@
         </is>
       </c>
       <c r="N184" s="6" t="n">
-        <v>70.94119195375541</v>
+        <v>73.28606809382831</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14708,7 +14510,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14745,7 +14547,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14778,7 +14580,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>73.28606809382831</v>
+        <v>73.9008893155349</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14787,7 +14589,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14824,7 +14626,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14857,7 +14659,7 @@
         </is>
       </c>
       <c r="N186" s="6" t="n">
-        <v>73.9008893155349</v>
+        <v>72.7246397114189</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14866,7 +14668,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14903,7 +14705,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14936,7 +14738,7 @@
         </is>
       </c>
       <c r="N187" s="6" t="n">
-        <v>72.7246397114189</v>
+        <v>72.7965497875051</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
@@ -14945,7 +14747,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14982,7 +14784,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -15015,7 +14817,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>72.7965497875051</v>
+        <v>71.6609231333517</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -15024,7 +14826,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15061,7 +14863,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -15094,7 +14896,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>71.6609231333517</v>
+        <v>67.242625937084</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -15103,7 +14905,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15140,7 +14942,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -15173,7 +14975,7 @@
         </is>
       </c>
       <c r="N190" s="6" t="n">
-        <v>67.242625937084</v>
+        <v>70.7004672541846</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -15182,7 +14984,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15219,7 +15021,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15252,7 +15054,7 @@
         </is>
       </c>
       <c r="N191" s="6" t="n">
-        <v>70.7004672541846</v>
+        <v>67.0600784236679</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15298,7 +15100,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15331,7 +15133,7 @@
         </is>
       </c>
       <c r="N192" s="6" t="n">
-        <v>67.0600784236679</v>
+        <v>65.96440553278519</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -15340,7 +15142,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15377,7 +15179,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15410,7 +15212,7 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>65.96440553278519</v>
+        <v>77.5369122989602</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
@@ -15419,7 +15221,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15456,7 +15258,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15489,7 +15291,7 @@
         </is>
       </c>
       <c r="N194" s="6" t="n">
-        <v>77.5369122989602</v>
+        <v>65.53966478494149</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
@@ -15498,7 +15300,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15535,7 +15337,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15568,7 +15370,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>65.53966478494149</v>
+        <v>62.32403609516</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15577,7 +15379,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15614,7 +15416,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15647,7 +15449,7 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>62.32403609516</v>
+        <v>51.4746640846626</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15656,7 +15458,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15693,7 +15495,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15726,7 +15528,7 @@
         </is>
       </c>
       <c r="N197" s="6" t="n">
-        <v>51.4746640846626</v>
+        <v>63.2932794208759</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
@@ -15735,7 +15537,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15772,7 +15574,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15805,7 +15607,7 @@
         </is>
       </c>
       <c r="N198" s="6" t="n">
-        <v>63.2932794208759</v>
+        <v>65.9218035546249</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -15814,7 +15616,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15653,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15884,7 +15686,7 @@
         </is>
       </c>
       <c r="N199" s="6" t="n">
-        <v>65.9218035546249</v>
+        <v>84.45121523562889</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
@@ -15893,7 +15695,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15930,7 +15732,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15963,7 +15765,7 @@
         </is>
       </c>
       <c r="N200" s="6" t="n">
-        <v>84.45121523562889</v>
+        <v>81.72207575243419</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
@@ -15972,7 +15774,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16009,7 +15811,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -16041,9 +15843,7 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N201" s="6" t="n">
-        <v>81.72207575243419</v>
-      </c>
+      <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16051,7 +15851,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16088,7 +15888,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -16128,7 +15928,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16165,7 +15965,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16205,7 +16005,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16242,7 +16042,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16282,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16319,7 +16119,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16333,22 +16133,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>electricidad</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.RNEW.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16359,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16396,7 +16196,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16436,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16473,7 +16273,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16513,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16550,7 +16350,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16590,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16627,7 +16427,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16667,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16704,7 +16504,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16744,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16781,7 +16581,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16821,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16858,7 +16658,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16898,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16935,7 +16735,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16975,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17012,7 +16812,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -17052,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +16889,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -17129,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17166,7 +16966,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17206,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17243,7 +17043,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17283,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17320,7 +17120,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17360,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17397,7 +17197,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17437,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17474,7 +17274,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17514,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17551,7 +17351,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17591,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17628,7 +17428,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17668,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17705,7 +17505,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17745,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17782,7 +17582,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17822,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17859,7 +17659,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17899,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17936,7 +17736,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17976,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18013,7 +17813,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -18053,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18090,7 +17890,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -18130,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18167,7 +17967,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18207,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18244,7 +18044,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18284,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18321,7 +18121,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18361,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18398,7 +18198,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18438,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18475,7 +18275,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18515,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18552,7 +18352,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18592,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18629,7 +18429,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18661,7 +18461,9 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n"/>
+      <c r="N235" s="6" t="n">
+        <v>1997.56479057799</v>
+      </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18669,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18706,7 +18508,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18739,7 +18541,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>1997.56479057799</v>
+        <v>2037.30182520885</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18748,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18785,7 +18587,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18818,7 +18620,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>2037.30182520885</v>
+        <v>2226.55481105961</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18827,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18864,7 +18666,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18897,7 +18699,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>2226.55481105961</v>
+        <v>2027.59967205093</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18906,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18943,7 +18745,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18976,7 +18778,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>2027.59967205093</v>
+        <v>2299.11785137022</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18985,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19022,7 +18824,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -19055,7 +18857,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>2299.11785137022</v>
+        <v>2111.33770063193</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -19064,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19101,7 +18903,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -19134,7 +18936,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>2111.33770063193</v>
+        <v>2203.62644762536</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -19143,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19180,7 +18982,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19213,7 +19015,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>2203.62644762536</v>
+        <v>2149.90770739915</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19222,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19259,7 +19061,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19292,7 +19094,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>2149.90770739915</v>
+        <v>2218.43187719732</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19301,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19338,7 +19140,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19371,7 +19173,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>2218.43187719732</v>
+        <v>2399.16210710328</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19380,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19417,7 +19219,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19450,7 +19252,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>2399.16210710328</v>
+        <v>2391.36796026802</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19459,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19496,7 +19298,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19529,7 +19331,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>2391.36796026802</v>
+        <v>2188.40606705914</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19538,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19575,7 +19377,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19608,7 +19410,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>2188.40606705914</v>
+        <v>2648.88652521803</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19617,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19654,7 +19456,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19687,7 +19489,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>2648.88652521803</v>
+        <v>2432.12630470112</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19696,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19733,7 +19535,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19766,7 +19568,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>2432.12630470112</v>
+        <v>2305.02805179379</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19775,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19812,7 +19614,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19845,7 +19647,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>2305.02805179379</v>
+        <v>2371.58340737061</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19854,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19891,7 +19693,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19924,7 +19726,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>2371.58340737061</v>
+        <v>2377.64028480756</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19933,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19970,7 +19772,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -20003,7 +19805,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>2377.64028480756</v>
+        <v>2391.33788149518</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -20012,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20049,7 +19851,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -20082,7 +19884,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>2391.33788149518</v>
+        <v>2346.01163837283</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -20091,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20128,7 +19930,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -20161,7 +19963,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>2346.01163837283</v>
+        <v>2231.75458660546</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -20170,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20207,7 +20009,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20240,7 +20042,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>2231.75458660546</v>
+        <v>2621.20702328211</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20249,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20286,7 +20088,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20319,7 +20121,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>2621.20702328211</v>
+        <v>2309.9066118944</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20328,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20365,7 +20167,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20398,7 +20200,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>2309.9066118944</v>
+        <v>2310.75269478151</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20407,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20444,7 +20246,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20477,7 +20279,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>2310.75269478151</v>
+        <v>2529.2097489945</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20486,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20523,7 +20325,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20556,7 +20358,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>2529.2097489945</v>
+        <v>2173.57093050952</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20565,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20602,7 +20404,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20635,7 +20437,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>2173.57093050952</v>
+        <v>2098.46944015591</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20644,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20681,7 +20483,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20714,7 +20516,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>2098.46944015591</v>
+        <v>2009.0681450604</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20723,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20760,7 +20562,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20793,7 +20595,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>2009.0681450604</v>
+        <v>1933.19114696252</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20802,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20839,7 +20641,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20872,7 +20674,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>1933.19114696252</v>
+        <v>1451.3949056587</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20881,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20918,7 +20720,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20951,7 +20753,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>1451.3949056587</v>
+        <v>1379.73439965</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20960,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20997,7 +20799,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -21030,7 +20832,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>1379.73439965</v>
+        <v>1093.43160664363</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -21039,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21076,7 +20878,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -21109,7 +20911,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>1093.43160664363</v>
+        <v>1409.82623845927</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -21118,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21155,7 +20957,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -21188,7 +20990,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>1409.82623845927</v>
+        <v>1364.68351163595</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -21197,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21234,7 +21036,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21267,7 +21069,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>1364.68351163595</v>
+        <v>1331.23284099658</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21276,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21313,7 +21115,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21345,9 +21147,7 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N269" s="6" t="n">
-        <v>1331.23284099658</v>
-      </c>
+      <c r="N269" s="4" t="n"/>
       <c r="O269" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21355,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21392,7 +21192,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21432,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21469,7 +21269,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21483,22 +21283,22 @@
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Recursos naturales</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>recursos_naturales</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>NY.GDP.TOTL.RT.ZS</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21509,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21546,7 +21346,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21586,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21623,7 +21423,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21663,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21700,7 +21500,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21740,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21777,7 +21577,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21817,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21854,7 +21654,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21894,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21931,7 +21731,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21971,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22008,7 +21808,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -22048,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22085,7 +21885,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -22125,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22162,7 +21962,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22202,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22239,7 +22039,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22271,7 +22071,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N281" s="4" t="n"/>
+      <c r="N281" s="6" t="n">
+        <v>5.48772130601331</v>
+      </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22279,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22316,7 +22118,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22349,7 +22151,7 @@
         </is>
       </c>
       <c r="N282" s="6" t="n">
-        <v>5.48772130601331</v>
+        <v>7.38794104909662</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
@@ -22358,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22395,7 +22197,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22428,7 +22230,7 @@
         </is>
       </c>
       <c r="N283" s="6" t="n">
-        <v>7.38794104909662</v>
+        <v>7.19271915747182</v>
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
@@ -22437,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22474,7 +22276,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22507,7 +22309,7 @@
         </is>
       </c>
       <c r="N284" s="6" t="n">
-        <v>7.19271915747182</v>
+        <v>10.7554427076038</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
@@ -22516,7 +22318,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22553,7 +22355,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22586,7 +22388,7 @@
         </is>
       </c>
       <c r="N285" s="6" t="n">
-        <v>10.7554427076038</v>
+        <v>33.9478841729493</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
@@ -22595,7 +22397,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22632,7 +22434,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22665,7 +22467,7 @@
         </is>
       </c>
       <c r="N286" s="6" t="n">
-        <v>33.9478841729493</v>
+        <v>24.8915014056924</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
@@ -22674,7 +22476,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22711,7 +22513,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22744,7 +22546,7 @@
         </is>
       </c>
       <c r="N287" s="6" t="n">
-        <v>24.8915014056924</v>
+        <v>22.9931513860828</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
@@ -22753,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22790,7 +22592,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22823,7 +22625,7 @@
         </is>
       </c>
       <c r="N288" s="6" t="n">
-        <v>22.9931513860828</v>
+        <v>16.1985343555775</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
@@ -22832,7 +22634,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22869,7 +22671,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22902,7 +22704,7 @@
         </is>
       </c>
       <c r="N289" s="6" t="n">
-        <v>16.1985343555775</v>
+        <v>15.8263995123574</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
@@ -22911,7 +22713,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22948,7 +22750,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22981,7 +22783,7 @@
         </is>
       </c>
       <c r="N290" s="6" t="n">
-        <v>15.8263995123574</v>
+        <v>36.481380981255</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
@@ -22990,7 +22792,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23027,7 +22829,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -23060,7 +22862,7 @@
         </is>
       </c>
       <c r="N291" s="6" t="n">
-        <v>36.481380981255</v>
+        <v>34.4312946645093</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
@@ -23069,7 +22871,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23106,7 +22908,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -23139,7 +22941,7 @@
         </is>
       </c>
       <c r="N292" s="6" t="n">
-        <v>34.4312946645093</v>
+        <v>24.750858904318</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
@@ -23148,7 +22950,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23185,7 +22987,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23218,7 +23020,7 @@
         </is>
       </c>
       <c r="N293" s="6" t="n">
-        <v>24.750858904318</v>
+        <v>13.1086608763643</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
@@ -23227,7 +23029,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23264,7 +23066,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23297,7 +23099,7 @@
         </is>
       </c>
       <c r="N294" s="6" t="n">
-        <v>13.1086608763643</v>
+        <v>17.0995109701258</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
@@ -23306,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23343,7 +23145,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23376,7 +23178,7 @@
         </is>
       </c>
       <c r="N295" s="6" t="n">
-        <v>17.0995109701258</v>
+        <v>19.0260300794035</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
@@ -23385,7 +23187,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23422,7 +23224,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23455,7 +23257,7 @@
         </is>
       </c>
       <c r="N296" s="6" t="n">
-        <v>19.0260300794035</v>
+        <v>16.3107385078032</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
@@ -23464,7 +23266,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23501,7 +23303,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23534,7 +23336,7 @@
         </is>
       </c>
       <c r="N297" s="6" t="n">
-        <v>16.3107385078032</v>
+        <v>8.00102414924425</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
@@ -23543,7 +23345,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23580,7 +23382,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23613,7 +23415,7 @@
         </is>
       </c>
       <c r="N298" s="6" t="n">
-        <v>8.00102414924425</v>
+        <v>15.9166311155573</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
@@ -23622,7 +23424,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23659,7 +23461,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23692,7 +23494,7 @@
         </is>
       </c>
       <c r="N299" s="6" t="n">
-        <v>15.9166311155573</v>
+        <v>10.0130859589153</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
@@ -23701,7 +23503,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23738,7 +23540,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23771,7 +23573,7 @@
         </is>
       </c>
       <c r="N300" s="6" t="n">
-        <v>10.0130859589153</v>
+        <v>20.9626504331607</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
@@ -23780,7 +23582,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23817,7 +23619,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23850,7 +23652,7 @@
         </is>
       </c>
       <c r="N301" s="6" t="n">
-        <v>20.9626504331607</v>
+        <v>29.2548511239111</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
@@ -23859,7 +23661,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23896,7 +23698,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23929,7 +23731,7 @@
         </is>
       </c>
       <c r="N302" s="6" t="n">
-        <v>29.2548511239111</v>
+        <v>16.6639894189064</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
@@ -23938,7 +23740,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23975,7 +23777,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -24008,7 +23810,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>16.6639894189064</v>
+        <v>15.7571776112482</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -24017,7 +23819,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24054,7 +23856,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -24087,7 +23889,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>15.7571776112482</v>
+        <v>15.7932181812518</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -24096,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24133,7 +23935,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -24166,7 +23968,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>15.7932181812518</v>
+        <v>16.2198265911409</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -24175,7 +23977,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24212,7 +24014,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24245,7 +24047,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>16.2198265911409</v>
+        <v>15.1363210095652</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24254,7 +24056,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24291,7 +24093,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24324,7 +24126,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>15.1363210095652</v>
+        <v>23.8367720643582</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24333,7 +24135,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24370,7 +24172,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24403,7 +24205,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>23.8367720643582</v>
+        <v>18.0963540802062</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24412,7 +24214,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24449,7 +24251,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24482,7 +24284,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>18.0963540802062</v>
+        <v>9.06347009522954</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24491,7 +24293,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24528,7 +24330,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24561,7 +24363,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>9.06347009522954</v>
+        <v>13.269532614572</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24570,7 +24372,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24607,7 +24409,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24640,7 +24442,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>13.269532614572</v>
+        <v>20.5761295010598</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24649,7 +24451,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24686,7 +24488,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24719,7 +24521,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>20.5761295010598</v>
+        <v>15.3442903568827</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24728,7 +24530,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24765,7 +24567,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24798,7 +24600,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>15.3442903568827</v>
+        <v>19.4545884689745</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24807,7 +24609,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24844,7 +24646,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24877,7 +24679,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>19.4545884689745</v>
+        <v>21.8955843439596</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24886,7 +24688,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24923,7 +24725,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24956,7 +24758,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>21.8955843439596</v>
+        <v>23.8297115705399</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24965,7 +24767,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25002,7 +24804,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -25035,7 +24837,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>23.8297115705399</v>
+        <v>29.2230041014033</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -25044,7 +24846,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25081,7 +24883,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -25114,7 +24916,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>29.2230041014033</v>
+        <v>28.0774680117788</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -25123,7 +24925,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25160,7 +24962,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -25193,7 +24995,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>28.0774680117788</v>
+        <v>23.1186941835454</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25202,7 +25004,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25239,7 +25041,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25272,7 +25074,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>23.1186941835454</v>
+        <v>23.9223070628002</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25281,7 +25083,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25318,7 +25120,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25351,7 +25153,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>23.9223070628002</v>
+        <v>10.5416668243022</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25360,7 +25162,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25397,7 +25199,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25430,7 +25232,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>10.5416668243022</v>
+        <v>12.380878328857</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25439,7 +25241,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25476,7 +25278,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25509,7 +25311,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>12.380878328857</v>
+        <v>24.4753357613612</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25518,7 +25320,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25555,7 +25357,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25588,7 +25390,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>24.4753357613612</v>
+        <v>18.7812359044725</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25597,7 +25399,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25634,7 +25436,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25667,7 +25469,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>18.7812359044725</v>
+        <v>17.6253449138361</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25676,7 +25478,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25713,7 +25515,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25746,7 +25548,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>17.6253449138361</v>
+        <v>11.8465082797294</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25755,7 +25557,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25792,7 +25594,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25824,9 +25626,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N326" s="6" t="n">
-        <v>11.8465082797294</v>
-      </c>
+      <c r="N326" s="4" t="n"/>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25834,7 +25634,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25871,7 +25671,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25911,7 +25711,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25948,7 +25748,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25988,7 +25788,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26025,7 +25825,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -26065,7 +25865,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26102,7 +25902,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -26142,7 +25942,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26179,7 +25979,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26219,7 +26019,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26256,7 +26056,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26296,7 +26096,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26333,7 +26133,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26373,7 +26173,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26410,7 +26210,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26450,7 +26250,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26487,7 +26287,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26527,7 +26327,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26564,7 +26364,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26604,87 +26404,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Energía y ambiente</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>energia_y_ambiente</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Recursos naturales</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>recursos_naturales</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N337" s="4" t="n"/>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26766,7 +26489,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26510,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12399,7 +12399,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22318,7 +22318,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22713,7 +22713,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22792,7 +22792,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22871,7 +22871,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23187,7 +23187,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23266,7 +23266,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23503,7 +23503,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23740,7 +23740,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23819,7 +23819,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23977,7 +23977,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24056,7 +24056,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24135,7 +24135,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24372,7 +24372,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24451,7 +24451,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24530,7 +24530,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24688,7 +24688,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24925,7 +24925,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25004,7 +25004,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25162,7 +25162,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25320,7 +25320,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25557,7 +25557,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25634,7 +25634,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25942,7 +25942,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26173,7 +26173,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26250,7 +26250,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26489,7 +26489,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q336"/>
+  <dimension ref="A1:Q337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,10 +715,14 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -792,10 +796,14 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -869,10 +877,14 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -946,10 +958,14 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1023,10 +1039,14 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1100,10 +1120,14 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1177,10 +1201,14 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1254,10 +1282,14 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1331,10 +1363,14 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1408,10 +1444,14 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1485,10 +1525,14 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1562,10 +1606,14 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1639,10 +1687,14 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1716,10 +1768,14 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1793,10 +1849,14 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1870,10 +1930,14 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1947,10 +2011,14 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2024,10 +2092,14 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2101,10 +2173,14 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2178,10 +2254,14 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2255,10 +2335,14 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2332,10 +2416,14 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2409,10 +2497,14 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2486,10 +2578,14 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2563,10 +2659,14 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2640,10 +2740,14 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2717,10 +2821,14 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2794,10 +2902,14 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2871,10 +2983,14 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2948,10 +3064,14 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3017,9 +3137,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N37" s="6" t="n">
-        <v>58.9830508474576</v>
-      </c>
+      <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3027,10 +3145,14 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3096,9 +3218,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>58.6571056062582</v>
-      </c>
+      <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3106,10 +3226,14 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3175,9 +3299,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
-        <v>58.3311603650587</v>
-      </c>
+      <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3185,10 +3307,14 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3254,9 +3380,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N40" s="6" t="n">
-        <v>58.0052151238592</v>
-      </c>
+      <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3264,10 +3388,14 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3333,9 +3461,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N41" s="6" t="n">
-        <v>57.6792698826597</v>
-      </c>
+      <c r="N41" s="4" t="n"/>
       <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3343,10 +3469,14 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3412,9 +3542,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>57.3533246414602</v>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3422,10 +3550,14 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3491,9 +3623,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N43" s="6" t="n">
-        <v>57.0273794002608</v>
-      </c>
+      <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3501,10 +3631,14 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3570,9 +3704,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N44" s="6" t="n">
-        <v>56.7014341590613</v>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3580,10 +3712,14 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3649,9 +3785,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
-        <v>56.3754889178618</v>
-      </c>
+      <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3659,10 +3793,14 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -3728,9 +3866,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>56.0495436766623</v>
-      </c>
+      <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3738,10 +3874,14 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3807,9 +3947,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N47" s="6" t="n">
-        <v>55.7235984354628</v>
-      </c>
+      <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3817,10 +3955,14 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -3886,9 +4028,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N48" s="6" t="n">
-        <v>55.53698769911</v>
-      </c>
+      <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3896,10 +4036,14 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -3965,9 +4109,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N49" s="6" t="n">
-        <v>55.3503769627572</v>
-      </c>
+      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3975,10 +4117,14 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4044,9 +4190,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N50" s="6" t="n">
-        <v>55.1637662264044</v>
-      </c>
+      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4054,10 +4198,14 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4123,9 +4271,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N51" s="6" t="n">
-        <v>54.9771554900516</v>
-      </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4133,10 +4279,14 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4202,9 +4352,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>54.7905447536988</v>
-      </c>
+      <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4212,10 +4360,14 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4281,9 +4433,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
-        <v>54.603934017346</v>
-      </c>
+      <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4291,10 +4441,14 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4360,9 +4514,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N54" s="6" t="n">
-        <v>54.4173232809931</v>
-      </c>
+      <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4370,10 +4522,14 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4439,9 +4595,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N55" s="6" t="n">
-        <v>54.2307125446403</v>
-      </c>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4449,10 +4603,14 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4518,9 +4676,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>54.0441018082875</v>
-      </c>
+      <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4528,10 +4684,14 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4597,9 +4757,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N57" s="6" t="n">
-        <v>53.8574910719347</v>
-      </c>
+      <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4607,10 +4765,14 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4676,9 +4838,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>53.6711070800975</v>
-      </c>
+      <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4686,10 +4846,14 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4755,9 +4919,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N59" s="6" t="n">
-        <v>53.4847230882603</v>
-      </c>
+      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4765,10 +4927,14 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -4834,9 +5000,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N60" s="6" t="n">
-        <v>53.2983390964231</v>
-      </c>
+      <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4844,10 +5008,14 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -4913,9 +5081,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N61" s="6" t="n">
-        <v>53.1119551045859</v>
-      </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4923,10 +5089,14 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -4992,9 +5162,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N62" s="6" t="n">
-        <v>52.9255711127487</v>
-      </c>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5002,10 +5170,14 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5071,9 +5243,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>52.7671447196871</v>
-      </c>
+      <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5081,10 +5251,14 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5150,9 +5324,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N64" s="6" t="n">
-        <v>52.6366759254011</v>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5160,10 +5332,14 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5229,9 +5405,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
-        <v>52.5341647298906</v>
-      </c>
+      <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5239,10 +5413,14 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5308,9 +5486,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N66" s="6" t="n">
-        <v>52.4596111331557</v>
-      </c>
+      <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5318,10 +5494,14 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q66" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5387,9 +5567,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
-        <v>52.4130151351964</v>
-      </c>
+      <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5397,10 +5575,14 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q67" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5466,9 +5648,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N68" s="6" t="n">
-        <v>52.3477807380534</v>
-      </c>
+      <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5476,10 +5656,14 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5545,9 +5729,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
-        <v>52.2949719403662</v>
-      </c>
+      <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5555,10 +5737,14 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5624,9 +5810,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
-        <v>52.2338793719177</v>
-      </c>
+      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5634,10 +5818,14 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5711,10 +5899,14 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q71" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5788,10 +5980,14 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5825,7 +6021,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -5839,22 +6035,22 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Bosques</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>electricidad</t>
+          <t>bosques</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.ACCS.ZS</t>
+          <t>AG.LND.FRST.ZS</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>Acceso a electricidad</t>
+          <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
       <c r="N73" s="4" t="n"/>
@@ -5865,10 +6061,14 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="n"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5902,7 +6102,7 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -5942,7 +6142,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +6179,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -6019,7 +6219,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6256,7 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -6096,7 +6296,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6333,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -6173,7 +6373,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6410,7 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -6250,7 +6450,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6487,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -6327,7 +6527,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6564,7 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -6404,7 +6604,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6641,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -6481,7 +6681,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6718,7 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -6558,7 +6758,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6795,7 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -6635,7 +6835,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6672,7 +6872,7 @@
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -6712,7 +6912,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6749,7 +6949,7 @@
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -6789,7 +6989,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6826,7 +7026,7 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -6866,7 +7066,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6903,7 +7103,7 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -6943,7 +7143,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6980,7 +7180,7 @@
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -7020,7 +7220,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7057,7 +7257,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -7097,7 +7297,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7134,7 +7334,7 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -7174,7 +7374,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7211,7 +7411,7 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -7251,7 +7451,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7288,7 +7488,7 @@
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7528,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7365,7 +7565,7 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -7405,7 +7605,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7642,7 @@
         </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
@@ -7482,7 +7682,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7719,7 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -7559,7 +7759,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7796,7 @@
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -7636,7 +7836,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7873,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -7713,7 +7913,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7950,7 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -7790,7 +7990,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +8027,7 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -7867,7 +8067,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7904,7 +8104,7 @@
         </is>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -7944,7 +8144,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7981,7 +8181,7 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -8021,7 +8221,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8058,7 +8258,7 @@
         </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -8098,7 +8298,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8135,7 +8335,7 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -8175,7 +8375,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8212,7 +8412,7 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -8252,7 +8452,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8289,7 +8489,7 @@
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -8321,9 +8521,7 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N105" s="6" t="n">
-        <v>97.82020300000001</v>
-      </c>
+      <c r="N105" s="4" t="n"/>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8331,7 +8529,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8368,7 +8566,7 @@
         </is>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -8401,7 +8599,7 @@
         </is>
       </c>
       <c r="N106" s="6" t="n">
-        <v>98.2395324707031</v>
+        <v>97.82020300000001</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
@@ -8410,7 +8608,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8447,7 +8645,7 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8480,7 +8678,7 @@
         </is>
       </c>
       <c r="N107" s="6" t="n">
-        <v>98.3233337402344</v>
+        <v>98.2395324707031</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
@@ -8489,7 +8687,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8526,7 +8724,7 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -8558,8 +8756,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N108" s="5" t="n">
-        <v>99</v>
+      <c r="N108" s="6" t="n">
+        <v>98.3233337402344</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
@@ -8568,7 +8766,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8803,7 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -8637,8 +8835,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N109" s="6" t="n">
-        <v>98.484130859375</v>
+      <c r="N109" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
@@ -8647,7 +8845,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8684,7 +8882,7 @@
         </is>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
@@ -8717,7 +8915,7 @@
         </is>
       </c>
       <c r="N110" s="6" t="n">
-        <v>98.7</v>
+        <v>98.484130859375</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
@@ -8726,7 +8924,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8763,7 +8961,7 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -8796,7 +8994,7 @@
         </is>
       </c>
       <c r="N111" s="6" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
@@ -8805,7 +9003,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8842,7 +9040,7 @@
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -8875,7 +9073,7 @@
         </is>
       </c>
       <c r="N112" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
@@ -8884,7 +9082,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8921,7 +9119,7 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -8963,7 +9161,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9000,7 +9198,7 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -9033,7 +9231,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
@@ -9042,7 +9240,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9079,7 +9277,7 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -9112,7 +9310,7 @@
         </is>
       </c>
       <c r="N115" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
@@ -9121,7 +9319,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9158,7 +9356,7 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -9191,7 +9389,7 @@
         </is>
       </c>
       <c r="N116" s="6" t="n">
-        <v>95.7</v>
+        <v>99.8</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
@@ -9200,7 +9398,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9237,7 +9435,7 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -9270,7 +9468,7 @@
         </is>
       </c>
       <c r="N117" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
@@ -9279,7 +9477,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9316,7 +9514,7 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -9349,7 +9547,7 @@
         </is>
       </c>
       <c r="N118" s="6" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
@@ -9358,7 +9556,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9395,7 +9593,7 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -9428,7 +9626,7 @@
         </is>
       </c>
       <c r="N119" s="6" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
@@ -9437,7 +9635,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9474,7 +9672,7 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -9507,7 +9705,7 @@
         </is>
       </c>
       <c r="N120" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -9516,7 +9714,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9553,7 +9751,7 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -9595,7 +9793,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9632,7 +9830,7 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
@@ -9664,8 +9862,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N122" s="5" t="n">
-        <v>99</v>
+      <c r="N122" s="6" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
@@ -9674,7 +9872,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9711,7 +9909,7 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -9743,8 +9941,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N123" s="6" t="n">
-        <v>99.09999999999999</v>
+      <c r="N123" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
@@ -9753,7 +9951,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9790,7 +9988,7 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
@@ -9823,7 +10021,7 @@
         </is>
       </c>
       <c r="N124" s="6" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
@@ -9832,7 +10030,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9869,7 +10067,7 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -9902,7 +10100,7 @@
         </is>
       </c>
       <c r="N125" s="6" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
@@ -9911,7 +10109,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9948,7 +10146,7 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
@@ -9981,7 +10179,7 @@
         </is>
       </c>
       <c r="N126" s="6" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
@@ -9990,7 +10188,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10027,7 +10225,7 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -10059,8 +10257,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N127" s="5" t="n">
-        <v>100</v>
+      <c r="N127" s="6" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
@@ -10069,7 +10267,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10106,7 +10304,7 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
@@ -10148,7 +10346,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10185,7 +10383,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -10217,8 +10415,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N129" s="6" t="n">
-        <v>99.40000000000001</v>
+      <c r="N129" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
@@ -10227,7 +10425,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10264,7 +10462,7 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
@@ -10297,7 +10495,7 @@
         </is>
       </c>
       <c r="N130" s="6" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
@@ -10306,7 +10504,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10343,7 +10541,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -10376,7 +10574,7 @@
         </is>
       </c>
       <c r="N131" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
@@ -10385,7 +10583,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10422,7 +10620,7 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
@@ -10455,7 +10653,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
@@ -10464,7 +10662,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10501,7 +10699,7 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -10534,7 +10732,7 @@
         </is>
       </c>
       <c r="N133" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
@@ -10543,7 +10741,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10580,7 +10778,7 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
@@ -10612,8 +10810,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N134" s="5" t="n">
-        <v>100</v>
+      <c r="N134" s="6" t="n">
+        <v>99.90000000000001</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
@@ -10622,7 +10820,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10659,7 +10857,7 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -10701,7 +10899,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10738,7 +10936,7 @@
         </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
@@ -10780,7 +10978,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10817,7 +11015,7 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -10859,7 +11057,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10896,7 +11094,7 @@
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -10928,7 +11126,9 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N138" s="4" t="n"/>
+      <c r="N138" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10936,7 +11136,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10973,7 +11173,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -10997,12 +11197,12 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.RNEW.ZS</t>
+          <t>EG.ELC.ACCS.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
+          <t>Acceso a electricidad</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11013,7 +11213,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11050,7 +11250,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11090,7 +11290,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11127,7 +11327,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11167,7 +11367,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11204,7 +11404,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11244,7 +11444,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11281,7 +11481,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11321,7 +11521,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11358,7 +11558,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11398,7 +11598,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11435,7 +11635,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11475,7 +11675,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11512,7 +11712,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11552,7 +11752,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11589,7 +11789,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11629,7 +11829,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11666,7 +11866,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11706,7 +11906,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11743,7 +11943,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11783,7 +11983,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11820,7 +12020,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -11860,7 +12060,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11897,7 +12097,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -11937,7 +12137,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11974,7 +12174,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12014,7 +12214,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12051,7 +12251,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12091,7 +12291,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12128,7 +12328,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12168,7 +12368,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12205,7 +12405,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12245,7 +12445,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12282,7 +12482,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12322,7 +12522,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12359,7 +12559,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12399,7 +12599,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12436,7 +12636,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12476,7 +12676,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12513,7 +12713,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12553,7 +12753,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12590,7 +12790,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12630,7 +12830,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12667,7 +12867,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12707,7 +12907,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12744,7 +12944,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12784,7 +12984,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12821,7 +13021,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -12861,7 +13061,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12898,7 +13098,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -12938,7 +13138,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12975,7 +13175,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13015,7 +13215,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13052,7 +13252,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13092,7 +13292,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13129,7 +13329,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13169,7 +13369,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13206,7 +13406,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13246,7 +13446,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13283,7 +13483,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13315,9 +13515,7 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N169" s="6" t="n">
-        <v>62.3438579929536</v>
-      </c>
+      <c r="N169" s="4" t="n"/>
       <c r="O169" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13325,7 +13523,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13362,7 +13560,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13395,7 +13593,7 @@
         </is>
       </c>
       <c r="N170" s="6" t="n">
-        <v>70.3254022135561</v>
+        <v>62.3438579929536</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
@@ -13404,7 +13602,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13441,7 +13639,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13474,7 +13672,7 @@
         </is>
       </c>
       <c r="N171" s="6" t="n">
-        <v>70.09341637010679</v>
+        <v>70.3254022135561</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
@@ -13483,7 +13681,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13520,7 +13718,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13553,7 +13751,7 @@
         </is>
       </c>
       <c r="N172" s="6" t="n">
-        <v>68.42985212302899</v>
+        <v>70.09341637010679</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
@@ -13562,7 +13760,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13599,7 +13797,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13632,7 +13830,7 @@
         </is>
       </c>
       <c r="N173" s="6" t="n">
-        <v>72.0068519116553</v>
+        <v>68.42985212302899</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
@@ -13641,7 +13839,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13678,7 +13876,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13711,7 +13909,7 @@
         </is>
       </c>
       <c r="N174" s="6" t="n">
-        <v>70.0514663834654</v>
+        <v>72.0068519116553</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
@@ -13720,7 +13918,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13757,7 +13955,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13790,7 +13988,7 @@
         </is>
       </c>
       <c r="N175" s="6" t="n">
-        <v>71.237498015558</v>
+        <v>70.0514663834654</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
@@ -13799,7 +13997,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13836,7 +14034,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -13869,7 +14067,7 @@
         </is>
       </c>
       <c r="N176" s="6" t="n">
-        <v>73.359380003843</v>
+        <v>71.237498015558</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
@@ -13878,7 +14076,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13915,7 +14113,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -13948,7 +14146,7 @@
         </is>
       </c>
       <c r="N177" s="6" t="n">
-        <v>71.59649946849279</v>
+        <v>73.359380003843</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
@@ -13957,7 +14155,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13994,7 +14192,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14027,7 +14225,7 @@
         </is>
       </c>
       <c r="N178" s="6" t="n">
-        <v>75.1646552472619</v>
+        <v>71.59649946849279</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14036,7 +14234,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14073,7 +14271,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14106,7 +14304,7 @@
         </is>
       </c>
       <c r="N179" s="6" t="n">
-        <v>73.7484021531353</v>
+        <v>75.1646552472619</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
@@ -14115,7 +14313,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14152,7 +14350,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14185,7 +14383,7 @@
         </is>
       </c>
       <c r="N180" s="6" t="n">
-        <v>67.0679878826884</v>
+        <v>73.7484021531353</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
@@ -14194,7 +14392,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14231,7 +14429,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14264,7 +14462,7 @@
         </is>
       </c>
       <c r="N181" s="6" t="n">
-        <v>64.8151373949397</v>
+        <v>67.0679878826884</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
@@ -14273,7 +14471,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14310,7 +14508,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14343,7 +14541,7 @@
         </is>
       </c>
       <c r="N182" s="6" t="n">
-        <v>65.83572609414431</v>
+        <v>64.8151373949397</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
@@ -14352,7 +14550,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14389,7 +14587,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14422,7 +14620,7 @@
         </is>
       </c>
       <c r="N183" s="6" t="n">
-        <v>70.94119195375541</v>
+        <v>65.83572609414431</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
@@ -14431,7 +14629,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14468,7 +14666,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14501,7 +14699,7 @@
         </is>
       </c>
       <c r="N184" s="6" t="n">
-        <v>73.28606809382831</v>
+        <v>70.94119195375541</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14510,7 +14708,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14547,7 +14745,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14580,7 +14778,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>73.9008893155349</v>
+        <v>73.28606809382831</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14589,7 +14787,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14626,7 +14824,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14659,7 +14857,7 @@
         </is>
       </c>
       <c r="N186" s="6" t="n">
-        <v>72.7246397114189</v>
+        <v>73.9008893155349</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14668,7 +14866,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14705,7 +14903,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14738,7 +14936,7 @@
         </is>
       </c>
       <c r="N187" s="6" t="n">
-        <v>72.7965497875051</v>
+        <v>72.7246397114189</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
@@ -14747,7 +14945,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14784,7 +14982,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -14817,7 +15015,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>71.6609231333517</v>
+        <v>72.7965497875051</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -14826,7 +15024,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14863,7 +15061,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -14896,7 +15094,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>67.242625937084</v>
+        <v>71.6609231333517</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -14905,7 +15103,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14942,7 +15140,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -14975,7 +15173,7 @@
         </is>
       </c>
       <c r="N190" s="6" t="n">
-        <v>70.7004672541846</v>
+        <v>67.242625937084</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -14984,7 +15182,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15021,7 +15219,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15054,7 +15252,7 @@
         </is>
       </c>
       <c r="N191" s="6" t="n">
-        <v>67.0600784236679</v>
+        <v>70.7004672541846</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
@@ -15063,7 +15261,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15100,7 +15298,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15133,7 +15331,7 @@
         </is>
       </c>
       <c r="N192" s="6" t="n">
-        <v>65.96440553278519</v>
+        <v>67.0600784236679</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -15142,7 +15340,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15179,7 +15377,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15212,7 +15410,7 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>77.5369122989602</v>
+        <v>65.96440553278519</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
@@ -15221,7 +15419,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15258,7 +15456,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15291,7 +15489,7 @@
         </is>
       </c>
       <c r="N194" s="6" t="n">
-        <v>65.53966478494149</v>
+        <v>77.5369122989602</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
@@ -15300,7 +15498,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15337,7 +15535,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15370,7 +15568,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>62.32403609516</v>
+        <v>65.53966478494149</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15379,7 +15577,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15416,7 +15614,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15449,7 +15647,7 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>51.4746640846626</v>
+        <v>62.32403609516</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15458,7 +15656,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15495,7 +15693,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15528,7 +15726,7 @@
         </is>
       </c>
       <c r="N197" s="6" t="n">
-        <v>63.2932794208759</v>
+        <v>51.4746640846626</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
@@ -15537,7 +15735,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15574,7 +15772,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15607,7 +15805,7 @@
         </is>
       </c>
       <c r="N198" s="6" t="n">
-        <v>65.9218035546249</v>
+        <v>63.2932794208759</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -15616,7 +15814,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15653,7 +15851,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15686,7 +15884,7 @@
         </is>
       </c>
       <c r="N199" s="6" t="n">
-        <v>84.45121523562889</v>
+        <v>65.9218035546249</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
@@ -15695,7 +15893,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15732,7 +15930,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15765,7 +15963,7 @@
         </is>
       </c>
       <c r="N200" s="6" t="n">
-        <v>81.72207575243419</v>
+        <v>84.45121523562889</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
@@ -15774,7 +15972,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15811,7 +16009,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -15843,7 +16041,9 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n"/>
+      <c r="N201" s="6" t="n">
+        <v>81.72207575243419</v>
+      </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15851,7 +16051,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15888,7 +16088,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -15928,7 +16128,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15965,7 +16165,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16005,7 +16205,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16042,7 +16242,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16082,7 +16282,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16119,7 +16319,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16133,22 +16333,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16159,7 +16359,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16196,7 +16396,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16236,7 +16436,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16273,7 +16473,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16313,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16350,7 +16550,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16390,7 +16590,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16427,7 +16627,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16467,7 +16667,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16504,7 +16704,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16544,7 +16744,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16581,7 +16781,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16621,7 +16821,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16658,7 +16858,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16698,7 +16898,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16735,7 +16935,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16775,7 +16975,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16812,7 +17012,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -16852,7 +17052,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16889,7 +17089,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -16929,7 +17129,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16966,7 +17166,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17006,7 +17206,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17043,7 +17243,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17083,7 +17283,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17120,7 +17320,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17160,7 +17360,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17197,7 +17397,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17237,7 +17437,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17274,7 +17474,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17314,7 +17514,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17351,7 +17551,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17391,7 +17591,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17428,7 +17628,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17468,7 +17668,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17505,7 +17705,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17545,7 +17745,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17582,7 +17782,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17622,7 +17822,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17659,7 +17859,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17699,7 +17899,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17736,7 +17936,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17776,7 +17976,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17813,7 +18013,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -17853,7 +18053,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17890,7 +18090,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -17930,7 +18130,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17967,7 +18167,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18007,7 +18207,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18044,7 +18244,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18084,7 +18284,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18121,7 +18321,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18161,7 +18361,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18198,7 +18398,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18238,7 +18438,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18275,7 +18475,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18315,7 +18515,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18352,7 +18552,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18392,7 +18592,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18429,7 +18629,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18461,9 +18661,7 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N235" s="6" t="n">
-        <v>1997.56479057799</v>
-      </c>
+      <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18471,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18508,7 +18706,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18541,7 +18739,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>2037.30182520885</v>
+        <v>1997.56479057799</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18550,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18587,7 +18785,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18620,7 +18818,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>2226.55481105961</v>
+        <v>2037.30182520885</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18629,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18666,7 +18864,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18699,7 +18897,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>2027.59967205093</v>
+        <v>2226.55481105961</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18708,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18745,7 +18943,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18778,7 +18976,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>2299.11785137022</v>
+        <v>2027.59967205093</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18787,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18824,7 +19022,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -18857,7 +19055,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>2111.33770063193</v>
+        <v>2299.11785137022</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -18866,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18903,7 +19101,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -18936,7 +19134,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>2203.62644762536</v>
+        <v>2111.33770063193</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -18945,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18982,7 +19180,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19015,7 +19213,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>2149.90770739915</v>
+        <v>2203.62644762536</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19024,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19061,7 +19259,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19094,7 +19292,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>2218.43187719732</v>
+        <v>2149.90770739915</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19103,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19140,7 +19338,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19173,7 +19371,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>2399.16210710328</v>
+        <v>2218.43187719732</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19182,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19219,7 +19417,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19252,7 +19450,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>2391.36796026802</v>
+        <v>2399.16210710328</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19261,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19298,7 +19496,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19331,7 +19529,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>2188.40606705914</v>
+        <v>2391.36796026802</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19340,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19377,7 +19575,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19410,7 +19608,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>2648.88652521803</v>
+        <v>2188.40606705914</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19419,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19456,7 +19654,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19489,7 +19687,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>2432.12630470112</v>
+        <v>2648.88652521803</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19498,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19535,7 +19733,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19568,7 +19766,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>2305.02805179379</v>
+        <v>2432.12630470112</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19577,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19614,7 +19812,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19647,7 +19845,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>2371.58340737061</v>
+        <v>2305.02805179379</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19656,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19693,7 +19891,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19726,7 +19924,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>2377.64028480756</v>
+        <v>2371.58340737061</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19735,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19772,7 +19970,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -19805,7 +20003,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>2391.33788149518</v>
+        <v>2377.64028480756</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -19814,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19851,7 +20049,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -19884,7 +20082,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>2346.01163837283</v>
+        <v>2391.33788149518</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -19893,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19930,7 +20128,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -19963,7 +20161,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>2231.75458660546</v>
+        <v>2346.01163837283</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -19972,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20009,7 +20207,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20042,7 +20240,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>2621.20702328211</v>
+        <v>2231.75458660546</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20051,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20088,7 +20286,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20121,7 +20319,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>2309.9066118944</v>
+        <v>2621.20702328211</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20130,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20167,7 +20365,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20200,7 +20398,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>2310.75269478151</v>
+        <v>2309.9066118944</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20209,7 +20407,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20246,7 +20444,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20279,7 +20477,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>2529.2097489945</v>
+        <v>2310.75269478151</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20288,7 +20486,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20325,7 +20523,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20358,7 +20556,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>2173.57093050952</v>
+        <v>2529.2097489945</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20367,7 +20565,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20404,7 +20602,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20437,7 +20635,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>2098.46944015591</v>
+        <v>2173.57093050952</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20446,7 +20644,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20483,7 +20681,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20516,7 +20714,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>2009.0681450604</v>
+        <v>2098.46944015591</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20525,7 +20723,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20562,7 +20760,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20595,7 +20793,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>1933.19114696252</v>
+        <v>2009.0681450604</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20604,7 +20802,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20641,7 +20839,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20674,7 +20872,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>1451.3949056587</v>
+        <v>1933.19114696252</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20683,7 +20881,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20720,7 +20918,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20753,7 +20951,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>1379.73439965</v>
+        <v>1451.3949056587</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20762,7 +20960,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20799,7 +20997,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -20832,7 +21030,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>1093.43160664363</v>
+        <v>1379.73439965</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -20841,7 +21039,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20878,7 +21076,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -20911,7 +21109,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>1409.82623845927</v>
+        <v>1093.43160664363</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -20920,7 +21118,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20957,7 +21155,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -20990,7 +21188,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>1364.68351163595</v>
+        <v>1409.82623845927</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -20999,7 +21197,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21036,7 +21234,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21069,7 +21267,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>1331.23284099658</v>
+        <v>1364.68351163595</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21078,7 +21276,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21115,7 +21313,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21147,7 +21345,9 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n"/>
+      <c r="N269" s="6" t="n">
+        <v>1331.23284099658</v>
+      </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21155,7 +21355,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21192,7 +21392,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21232,7 +21432,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21269,7 +21469,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21283,22 +21483,22 @@
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>Recursos naturales</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>recursos_naturales</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21309,7 +21509,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21346,7 +21546,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21386,7 +21586,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21423,7 +21623,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21463,7 +21663,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21500,7 +21700,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21540,7 +21740,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21577,7 +21777,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21617,7 +21817,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21654,7 +21854,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21694,7 +21894,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21731,7 +21931,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21771,7 +21971,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21808,7 +22008,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -21848,7 +22048,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21885,7 +22085,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -21925,7 +22125,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21962,7 +22162,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22002,7 +22202,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22039,7 +22239,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22071,9 +22271,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N281" s="6" t="n">
-        <v>5.48772130601331</v>
-      </c>
+      <c r="N281" s="4" t="n"/>
       <c r="O281" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22081,7 +22279,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22118,7 +22316,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22151,7 +22349,7 @@
         </is>
       </c>
       <c r="N282" s="6" t="n">
-        <v>7.38794104909662</v>
+        <v>5.48772130601331</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
@@ -22160,7 +22358,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22197,7 +22395,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22230,7 +22428,7 @@
         </is>
       </c>
       <c r="N283" s="6" t="n">
-        <v>7.19271915747182</v>
+        <v>7.38794104909662</v>
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
@@ -22239,7 +22437,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22276,7 +22474,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22309,7 +22507,7 @@
         </is>
       </c>
       <c r="N284" s="6" t="n">
-        <v>10.7554427076038</v>
+        <v>7.19271915747182</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
@@ -22318,7 +22516,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22355,7 +22553,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22388,7 +22586,7 @@
         </is>
       </c>
       <c r="N285" s="6" t="n">
-        <v>33.9478841729493</v>
+        <v>10.7554427076038</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
@@ -22397,7 +22595,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22434,7 +22632,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22467,7 +22665,7 @@
         </is>
       </c>
       <c r="N286" s="6" t="n">
-        <v>24.8915014056924</v>
+        <v>33.9478841729493</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
@@ -22476,7 +22674,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22513,7 +22711,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22546,7 +22744,7 @@
         </is>
       </c>
       <c r="N287" s="6" t="n">
-        <v>22.9931513860828</v>
+        <v>24.8915014056924</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
@@ -22555,7 +22753,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22592,7 +22790,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22625,7 +22823,7 @@
         </is>
       </c>
       <c r="N288" s="6" t="n">
-        <v>16.1985343555775</v>
+        <v>22.9931513860828</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
@@ -22634,7 +22832,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22671,7 +22869,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22704,7 +22902,7 @@
         </is>
       </c>
       <c r="N289" s="6" t="n">
-        <v>15.8263995123574</v>
+        <v>16.1985343555775</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
@@ -22713,7 +22911,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22750,7 +22948,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22783,7 +22981,7 @@
         </is>
       </c>
       <c r="N290" s="6" t="n">
-        <v>36.481380981255</v>
+        <v>15.8263995123574</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
@@ -22792,7 +22990,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22829,7 +23027,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -22862,7 +23060,7 @@
         </is>
       </c>
       <c r="N291" s="6" t="n">
-        <v>34.4312946645093</v>
+        <v>36.481380981255</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
@@ -22871,7 +23069,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +23106,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -22941,7 +23139,7 @@
         </is>
       </c>
       <c r="N292" s="6" t="n">
-        <v>24.750858904318</v>
+        <v>34.4312946645093</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
@@ -22950,7 +23148,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22987,7 +23185,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23020,7 +23218,7 @@
         </is>
       </c>
       <c r="N293" s="6" t="n">
-        <v>13.1086608763643</v>
+        <v>24.750858904318</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
@@ -23029,7 +23227,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23066,7 +23264,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23099,7 +23297,7 @@
         </is>
       </c>
       <c r="N294" s="6" t="n">
-        <v>17.0995109701258</v>
+        <v>13.1086608763643</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
@@ -23108,7 +23306,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23145,7 +23343,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23178,7 +23376,7 @@
         </is>
       </c>
       <c r="N295" s="6" t="n">
-        <v>19.0260300794035</v>
+        <v>17.0995109701258</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
@@ -23187,7 +23385,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23224,7 +23422,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23257,7 +23455,7 @@
         </is>
       </c>
       <c r="N296" s="6" t="n">
-        <v>16.3107385078032</v>
+        <v>19.0260300794035</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
@@ -23266,7 +23464,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23303,7 +23501,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23336,7 +23534,7 @@
         </is>
       </c>
       <c r="N297" s="6" t="n">
-        <v>8.00102414924425</v>
+        <v>16.3107385078032</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
@@ -23345,7 +23543,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23382,7 +23580,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23415,7 +23613,7 @@
         </is>
       </c>
       <c r="N298" s="6" t="n">
-        <v>15.9166311155573</v>
+        <v>8.00102414924425</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
@@ -23424,7 +23622,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23461,7 +23659,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23494,7 +23692,7 @@
         </is>
       </c>
       <c r="N299" s="6" t="n">
-        <v>10.0130859589153</v>
+        <v>15.9166311155573</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
@@ -23503,7 +23701,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23540,7 +23738,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23573,7 +23771,7 @@
         </is>
       </c>
       <c r="N300" s="6" t="n">
-        <v>20.9626504331607</v>
+        <v>10.0130859589153</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
@@ -23582,7 +23780,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23619,7 +23817,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23652,7 +23850,7 @@
         </is>
       </c>
       <c r="N301" s="6" t="n">
-        <v>29.2548511239111</v>
+        <v>20.9626504331607</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
@@ -23661,7 +23859,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23698,7 +23896,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23731,7 +23929,7 @@
         </is>
       </c>
       <c r="N302" s="6" t="n">
-        <v>16.6639894189064</v>
+        <v>29.2548511239111</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
@@ -23740,7 +23938,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23777,7 +23975,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23810,7 +24008,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>15.7571776112482</v>
+        <v>16.6639894189064</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -23819,7 +24017,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23856,7 +24054,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -23889,7 +24087,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>15.7932181812518</v>
+        <v>15.7571776112482</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -23898,7 +24096,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23935,7 +24133,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -23968,7 +24166,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>16.2198265911409</v>
+        <v>15.7932181812518</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -23977,7 +24175,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24014,7 +24212,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24047,7 +24245,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>15.1363210095652</v>
+        <v>16.2198265911409</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24056,7 +24254,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24093,7 +24291,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24126,7 +24324,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>23.8367720643582</v>
+        <v>15.1363210095652</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24135,7 +24333,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24172,7 +24370,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24205,7 +24403,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>18.0963540802062</v>
+        <v>23.8367720643582</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24214,7 +24412,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24251,7 +24449,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24284,7 +24482,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>9.06347009522954</v>
+        <v>18.0963540802062</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24293,7 +24491,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24330,7 +24528,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24363,7 +24561,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>13.269532614572</v>
+        <v>9.06347009522954</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24372,7 +24570,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24409,7 +24607,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24442,7 +24640,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>20.5761295010598</v>
+        <v>13.269532614572</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24451,7 +24649,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24488,7 +24686,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24521,7 +24719,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>15.3442903568827</v>
+        <v>20.5761295010598</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24530,7 +24728,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24567,7 +24765,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24600,7 +24798,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>19.4545884689745</v>
+        <v>15.3442903568827</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24609,7 +24807,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24646,7 +24844,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24679,7 +24877,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>21.8955843439596</v>
+        <v>19.4545884689745</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24688,7 +24886,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24923,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24758,7 +24956,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>23.8297115705399</v>
+        <v>21.8955843439596</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24767,7 +24965,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24804,7 +25002,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24837,7 +25035,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>29.2230041014033</v>
+        <v>23.8297115705399</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -24846,7 +25044,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24883,7 +25081,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -24916,7 +25114,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>28.0774680117788</v>
+        <v>29.2230041014033</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -24925,7 +25123,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24962,7 +25160,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -24995,7 +25193,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>23.1186941835454</v>
+        <v>28.0774680117788</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25004,7 +25202,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25041,7 +25239,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25074,7 +25272,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>23.9223070628002</v>
+        <v>23.1186941835454</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25083,7 +25281,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25120,7 +25318,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25153,7 +25351,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>10.5416668243022</v>
+        <v>23.9223070628002</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25162,7 +25360,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25397,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25232,7 +25430,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>12.380878328857</v>
+        <v>10.5416668243022</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25241,7 +25439,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25278,7 +25476,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25311,7 +25509,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>24.4753357613612</v>
+        <v>12.380878328857</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25320,7 +25518,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25357,7 +25555,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25390,7 +25588,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>18.7812359044725</v>
+        <v>24.4753357613612</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25399,7 +25597,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25436,7 +25634,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25469,7 +25667,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>17.6253449138361</v>
+        <v>18.7812359044725</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25478,7 +25676,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25713,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25548,7 +25746,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>11.8465082797294</v>
+        <v>17.6253449138361</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25557,7 +25755,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25594,7 +25792,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25626,7 +25824,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="6" t="n">
+        <v>11.8465082797294</v>
+      </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25634,7 +25834,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25671,7 +25871,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25711,7 +25911,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25948,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25788,7 +25988,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +26025,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -25865,7 +26065,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +26102,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -25942,7 +26142,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +26179,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26019,7 +26219,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26256,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26096,7 +26296,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26333,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26173,7 +26373,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26410,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26250,7 +26450,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26487,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26327,7 +26527,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26564,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26404,10 +26604,87 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>Recursos naturales</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>recursos_naturales</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>NY.GDP.TOTL.RT.ZS</t>
+        </is>
+      </c>
+      <c r="M337" s="4" t="inlineStr">
+        <is>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="N337" s="4" t="n"/>
+      <c r="O337" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P337" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26489,7 +26766,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -26510,7 +26787,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
